--- a/StructureDefinition-SEEHDSLMAlertInformation.xlsx
+++ b/StructureDefinition-SEEHDSLMAlertInformation.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-06T07:04:04+00:00</t>
+    <t>2026-10-06T07:20:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-SEEHDSLMAlertInformation.xlsx
+++ b/StructureDefinition-SEEHDSLMAlertInformation.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-06T07:20:43+00:00</t>
+    <t>2026-10-07T11:41:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-SEEHDSLMAlertInformation.xlsx
+++ b/StructureDefinition-SEEHDSLMAlertInformation.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-07T11:41:58+00:00</t>
+    <t>2026-10-07T11:49:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-SEEHDSLMAlertInformation.xlsx
+++ b/StructureDefinition-SEEHDSLMAlertInformation.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3937" uniqueCount="370">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3903" uniqueCount="372">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-07T11:49:57+00:00</t>
+    <t>2026-10-09T07:52:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -263,8 +263,7 @@
     <t>Uppmärksamhetsinformation</t>
   </si>
   <si>
-    <t>Den uppmärksamhetsinformation som matchar begäran.
-Kardinalitet: Valfri, lista.</t>
+    <t>Den uppmärksamhetsinformation som matchar begäran.</t>
   </si>
   <si>
     <t xml:space="preserve">ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
@@ -357,8 +356,7 @@
   </si>
   <si>
     <t>Innehåller basinformation om dokumentet (PatientSummaryHeaderType).
-OBS: documentTitle, documentTime, nullified och nullifiedReason är N/A (0..0) för detta TK.
-Kardinalitet: Obligatorisk.</t>
+OBS: documentTitle, documentTime, nullified och nullifiedReason är N/A (0..0) för detta TK.</t>
   </si>
   <si>
     <t>SEEHDSLMAlertInformation.alertInformation.alertInformationHeader.id</t>
@@ -373,36 +371,60 @@
     <t>SEEHDSLMAlertInformation.alertInformation.alertInformationHeader.documentId</t>
   </si>
   <si>
+    <t xml:space="preserve">https://fhir.inera.se/ig/ehds-tk/StructureDefinition/SEEHDSRivString
+</t>
+  </si>
+  <si>
     <t>Dokumentets identitet</t>
   </si>
   <si>
-    <t>Dokumentets identitet som är unik inom källsystemet.
-Kardinalitet: Obligatorisk.</t>
+    <t>Dokumentets identitet som är unik inom källsystemet.</t>
   </si>
   <si>
     <t>SEEHDSLMAlertInformation.alertInformation.alertInformationHeader.sourceSystemHSAId</t>
   </si>
   <si>
-    <t xml:space="preserve">Identifier
+    <t>HSA-id för källsystem</t>
+  </si>
+  <si>
+    <t>HSA-id för det system som tillgängliggör informationen.</t>
+  </si>
+  <si>
+    <t>SEEHDSLMAlertInformation.alertInformation.alertInformationHeader.documentTitle</t>
+  </si>
+  <si>
+    <t>Titel</t>
+  </si>
+  <si>
+    <t>N/A</t>
+  </si>
+  <si>
+    <t>SEEHDSLMAlertInformation.alertInformation.alertInformationHeader.documentTime</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://fhir.inera.se/ig/ehds-tk/StructureDefinition/SEEHDSRivTimeStamp
 </t>
   </si>
   <si>
-    <t>HSA-id för källsystem</t>
-  </si>
-  <si>
-    <t>HSA-id för det system som tillgängliggör informationen.
-Kardinalitet: Obligatorisk.</t>
+    <t>Tidpunkt för dokumentet</t>
+  </si>
+  <si>
+    <t>N/A
+Format enligt XSD (TimeStampType): ÅÅÅÅMMDDttmmss.</t>
   </si>
   <si>
     <t>SEEHDSLMAlertInformation.alertInformation.alertInformationHeader.patientId</t>
   </si>
   <si>
+    <t xml:space="preserve">https://fhir.inera.se/ig/ehds-tk/StructureDefinition/SEEHDSRivPersonIdTypeHealthcondDescription2
+</t>
+  </si>
+  <si>
     <t>Patientidentifierare</t>
   </si>
   <si>
     <t>Identifierare för patient. id = patientens identifierare (12 tecken).
-type = OID för typ av identifierare.
-Kardinalitet: Obligatorisk.</t>
+type = OID för typ av identifierare.</t>
   </si>
   <si>
     <t>SEEHDSLMAlertInformation.alertInformation.alertInformationHeader.accountableHealthcareProfessional</t>
@@ -411,8 +433,7 @@
     <t>Ansvarig hälso- och sjukvårdsperson</t>
   </si>
   <si>
-    <t>Information om den hälso- och sjukvårdsperson som är ansvarig för informationen.
-Kardinalitet: Obligatorisk.</t>
+    <t>Information om den hälso- och sjukvårdsperson som är ansvarig för informationen.</t>
   </si>
   <si>
     <t>SEEHDSLMAlertInformation.alertInformation.alertInformationHeader.accountableHealthcareProfessional.id</t>
@@ -427,211 +448,191 @@
     <t>SEEHDSLMAlertInformation.alertInformation.alertInformationHeader.accountableHealthcareProfessional.authorTime</t>
   </si>
   <si>
-    <t xml:space="preserve">dateTime
+    <t>Tidpunkt för registrering</t>
+  </si>
+  <si>
+    <t>Tidpunkt då informationen registrerades. Format: YYYYMMDDhhmmss.
+Format enligt XSD (TimeStampType): ÅÅÅÅMMDDttmmss.</t>
+  </si>
+  <si>
+    <t>SEEHDSLMAlertInformation.alertInformation.alertInformationHeader.accountableHealthcareProfessional.healthcareProfessionalHSAId</t>
+  </si>
+  <si>
+    <t>HSA-id för hälso- och sjukvårdspersonal</t>
+  </si>
+  <si>
+    <t>HSA-id för hälso- och sjukvårdspersonal.</t>
+  </si>
+  <si>
+    <t>SEEHDSLMAlertInformation.alertInformation.alertInformationHeader.accountableHealthcareProfessional.healthcareProfessionalName</t>
+  </si>
+  <si>
+    <t>Namn</t>
+  </si>
+  <si>
+    <t>Namn på hälso- och sjukvårdspersonal.</t>
+  </si>
+  <si>
+    <t>SEEHDSLMAlertInformation.alertInformation.alertInformationHeader.accountableHealthcareProfessional.healthcareProfessionalRoleCode</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://fhir.inera.se/ig/ehds-tk/StructureDefinition/SEEHDSRivCVTypeHealthcondDescription2
 </t>
   </si>
   <si>
-    <t>Tidpunkt för registrering</t>
-  </si>
-  <si>
-    <t>Tidpunkt då informationen registrerades. Format: YYYYMMDDhhmmss.
-Kardinalitet: Obligatorisk.</t>
-  </si>
-  <si>
-    <t>SEEHDSLMAlertInformation.alertInformation.alertInformationHeader.accountableHealthcareProfessional.healthcareProfessionalHSAId</t>
-  </si>
-  <si>
-    <t>HSA-id för hälso- och sjukvårdspersonal</t>
-  </si>
-  <si>
-    <t>HSA-id för hälso- och sjukvårdspersonal.
-Kardinalitet: Valfri.</t>
-  </si>
-  <si>
-    <t>SEEHDSLMAlertInformation.alertInformation.alertInformationHeader.accountableHealthcareProfessional.healthcareProfessionalName</t>
-  </si>
-  <si>
-    <t>Namn</t>
-  </si>
-  <si>
-    <t>Namn på hälso- och sjukvårdspersonal.
-Kardinalitet: Valfri.</t>
-  </si>
-  <si>
-    <t>SEEHDSLMAlertInformation.alertInformation.alertInformationHeader.accountableHealthcareProfessional.healthcareProfessionalRoleCode</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CodeableConcept
+    <t>Befattning (CVType)</t>
+  </si>
+  <si>
+    <t>Information om personens befattning. KV Befattning (OID 1.2.752.129.2.2.1.4).</t>
+  </si>
+  <si>
+    <t>SEEHDSLMAlertInformation.alertInformation.alertInformationHeader.accountableHealthcareProfessional.healthcareProfessionalOrgUnit</t>
+  </si>
+  <si>
+    <t>Organisationsenhet</t>
+  </si>
+  <si>
+    <t>Den organisation som hälso- och sjukvårdspersonalen är uppdragstagare i.</t>
+  </si>
+  <si>
+    <t>SEEHDSLMAlertInformation.alertInformation.alertInformationHeader.accountableHealthcareProfessional.healthcareProfessionalOrgUnit.id</t>
+  </si>
+  <si>
+    <t>SEEHDSLMAlertInformation.alertInformation.alertInformationHeader.accountableHealthcareProfessional.healthcareProfessionalOrgUnit.extension</t>
+  </si>
+  <si>
+    <t>SEEHDSLMAlertInformation.alertInformation.alertInformationHeader.accountableHealthcareProfessional.healthcareProfessionalOrgUnit.modifierExtension</t>
+  </si>
+  <si>
+    <t>SEEHDSLMAlertInformation.alertInformation.alertInformationHeader.accountableHealthcareProfessional.healthcareProfessionalOrgUnit.orgUnitHSAId</t>
+  </si>
+  <si>
+    <t>HSA-id för organisationsenhet</t>
+  </si>
+  <si>
+    <t>HSA-id för organisationsenhet.</t>
+  </si>
+  <si>
+    <t>SEEHDSLMAlertInformation.alertInformation.alertInformationHeader.accountableHealthcareProfessional.healthcareProfessionalOrgUnit.orgUnitName</t>
+  </si>
+  <si>
+    <t>Namn på organisationsenhet</t>
+  </si>
+  <si>
+    <t>Namn på organisationsenhet.</t>
+  </si>
+  <si>
+    <t>SEEHDSLMAlertInformation.alertInformation.alertInformationHeader.accountableHealthcareProfessional.healthcareProfessionalOrgUnit.orgUnitTelecom</t>
+  </si>
+  <si>
+    <t>Telefon till organisationsenhet</t>
+  </si>
+  <si>
+    <t>Telefon till organisationsenhet.</t>
+  </si>
+  <si>
+    <t>SEEHDSLMAlertInformation.alertInformation.alertInformationHeader.accountableHealthcareProfessional.healthcareProfessionalOrgUnit.orgUnitEmail</t>
+  </si>
+  <si>
+    <t>Epost till organisationsenhet</t>
+  </si>
+  <si>
+    <t>Epost till organisationsenhet.</t>
+  </si>
+  <si>
+    <t>SEEHDSLMAlertInformation.alertInformation.alertInformationHeader.accountableHealthcareProfessional.healthcareProfessionalOrgUnit.orgUnitAddress</t>
+  </si>
+  <si>
+    <t>Postadress för organisationsenhet</t>
+  </si>
+  <si>
+    <t>Postadress för organisationsenhet.</t>
+  </si>
+  <si>
+    <t>SEEHDSLMAlertInformation.alertInformation.alertInformationHeader.accountableHealthcareProfessional.healthcareProfessionalOrgUnit.orgUnitLocation</t>
+  </si>
+  <si>
+    <t>Fysisk plats för organisationsenhet</t>
+  </si>
+  <si>
+    <t>Text som anger namn på plats eller ort för organisationens fysiska placering.</t>
+  </si>
+  <si>
+    <t>SEEHDSLMAlertInformation.alertInformation.alertInformationHeader.accountableHealthcareProfessional.healthcareProfessionalCareUnitHSAId</t>
+  </si>
+  <si>
+    <t>HSA-id för vårdenhet</t>
+  </si>
+  <si>
+    <t>HSA-id för vårdenhet. Se regel 1 i TKB.</t>
+  </si>
+  <si>
+    <t>SEEHDSLMAlertInformation.alertInformation.alertInformationHeader.accountableHealthcareProfessional.healthcareProfessionalCareGiverHSAId</t>
+  </si>
+  <si>
+    <t>HSA-id för vårdgivare</t>
+  </si>
+  <si>
+    <t>HSA-id för vårdgivaren.</t>
+  </si>
+  <si>
+    <t>SEEHDSLMAlertInformation.alertInformation.alertInformationHeader.legalAuthenticator</t>
+  </si>
+  <si>
+    <t>Signerande person</t>
+  </si>
+  <si>
+    <t>Information om vem som signerat informationen i dokumentet.</t>
+  </si>
+  <si>
+    <t>SEEHDSLMAlertInformation.alertInformation.alertInformationHeader.legalAuthenticator.id</t>
+  </si>
+  <si>
+    <t>SEEHDSLMAlertInformation.alertInformation.alertInformationHeader.legalAuthenticator.extension</t>
+  </si>
+  <si>
+    <t>SEEHDSLMAlertInformation.alertInformation.alertInformationHeader.legalAuthenticator.modifierExtension</t>
+  </si>
+  <si>
+    <t>SEEHDSLMAlertInformation.alertInformation.alertInformationHeader.legalAuthenticator.signatureTime</t>
+  </si>
+  <si>
+    <t>Tidpunkt för signering</t>
+  </si>
+  <si>
+    <t>Tidpunkt för signering. Format: YYYYMMDDhhmmss.
+Format enligt XSD (TimeStampType): ÅÅÅÅMMDDttmmss.</t>
+  </si>
+  <si>
+    <t>SEEHDSLMAlertInformation.alertInformation.alertInformationHeader.legalAuthenticator.legalAuthenticatorHSAId</t>
+  </si>
+  <si>
+    <t>HSA-id för signerande</t>
+  </si>
+  <si>
+    <t>HSA-id för person som signerat dokumentet.</t>
+  </si>
+  <si>
+    <t>SEEHDSLMAlertInformation.alertInformation.alertInformationHeader.legalAuthenticator.legalAuthenticatorName</t>
+  </si>
+  <si>
+    <t>Namn på signerande person</t>
+  </si>
+  <si>
+    <t>Namn i klartext för signerande person.</t>
+  </si>
+  <si>
+    <t>SEEHDSLMAlertInformation.alertInformation.alertInformationHeader.approvedForPatient</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://fhir.inera.se/ig/ehds-tk/StructureDefinition/SEEHDSRivBoolean
 </t>
   </si>
   <si>
-    <t>Befattning (CVType)</t>
-  </si>
-  <si>
-    <t>Information om personens befattning. KV Befattning (OID 1.2.752.129.2.2.1.4).
-Kardinalitet: Valfri.</t>
-  </si>
-  <si>
-    <t>SEEHDSLMAlertInformation.alertInformation.alertInformationHeader.accountableHealthcareProfessional.healthcareProfessionalOrgUnit</t>
-  </si>
-  <si>
-    <t>Organisationsenhet</t>
-  </si>
-  <si>
-    <t>Den organisation som hälso- och sjukvårdspersonalen är uppdragstagare i.
-Kardinalitet: Valfri.</t>
-  </si>
-  <si>
-    <t>SEEHDSLMAlertInformation.alertInformation.alertInformationHeader.accountableHealthcareProfessional.healthcareProfessionalOrgUnit.id</t>
-  </si>
-  <si>
-    <t>SEEHDSLMAlertInformation.alertInformation.alertInformationHeader.accountableHealthcareProfessional.healthcareProfessionalOrgUnit.extension</t>
-  </si>
-  <si>
-    <t>SEEHDSLMAlertInformation.alertInformation.alertInformationHeader.accountableHealthcareProfessional.healthcareProfessionalOrgUnit.modifierExtension</t>
-  </si>
-  <si>
-    <t>SEEHDSLMAlertInformation.alertInformation.alertInformationHeader.accountableHealthcareProfessional.healthcareProfessionalOrgUnit.orgUnitHSAId</t>
-  </si>
-  <si>
-    <t>HSA-id för organisationsenhet</t>
-  </si>
-  <si>
-    <t>HSA-id för organisationsenhet.
-Kardinalitet: Obligatorisk (inom OrgUnitType).</t>
-  </si>
-  <si>
-    <t>SEEHDSLMAlertInformation.alertInformation.alertInformationHeader.accountableHealthcareProfessional.healthcareProfessionalOrgUnit.orgUnitName</t>
-  </si>
-  <si>
-    <t>Namn på organisationsenhet</t>
-  </si>
-  <si>
-    <t>Namn på organisationsenhet.
-Kardinalitet: Obligatorisk (inom OrgUnitType).</t>
-  </si>
-  <si>
-    <t>SEEHDSLMAlertInformation.alertInformation.alertInformationHeader.accountableHealthcareProfessional.healthcareProfessionalOrgUnit.orgUnitTelecom</t>
-  </si>
-  <si>
-    <t>Telefon till organisationsenhet</t>
-  </si>
-  <si>
-    <t>Telefon till organisationsenhet.
-Kardinalitet: Valfri.</t>
-  </si>
-  <si>
-    <t>SEEHDSLMAlertInformation.alertInformation.alertInformationHeader.accountableHealthcareProfessional.healthcareProfessionalOrgUnit.orgUnitEmail</t>
-  </si>
-  <si>
-    <t>Epost till organisationsenhet</t>
-  </si>
-  <si>
-    <t>Epost till organisationsenhet.
-Kardinalitet: Valfri.</t>
-  </si>
-  <si>
-    <t>SEEHDSLMAlertInformation.alertInformation.alertInformationHeader.accountableHealthcareProfessional.healthcareProfessionalOrgUnit.orgUnitAddress</t>
-  </si>
-  <si>
-    <t>Postadress för organisationsenhet</t>
-  </si>
-  <si>
-    <t>Postadress för organisationsenhet.
-Kardinalitet: Valfri.</t>
-  </si>
-  <si>
-    <t>SEEHDSLMAlertInformation.alertInformation.alertInformationHeader.accountableHealthcareProfessional.healthcareProfessionalOrgUnit.orgUnitLocation</t>
-  </si>
-  <si>
-    <t>Fysisk plats för organisationsenhet</t>
-  </si>
-  <si>
-    <t>Text som anger namn på plats eller ort för organisationens fysiska placering.
-Kardinalitet: Valfri.</t>
-  </si>
-  <si>
-    <t>SEEHDSLMAlertInformation.alertInformation.alertInformationHeader.accountableHealthcareProfessional.healthcareProfessionalCareUnitHSAId</t>
-  </si>
-  <si>
-    <t>HSA-id för vårdenhet</t>
-  </si>
-  <si>
-    <t>HSA-id för vårdenhet. Se regel 1 i TKB.
-Kardinalitet: Valfri (villkorlig, se regel 1).</t>
-  </si>
-  <si>
-    <t>SEEHDSLMAlertInformation.alertInformation.alertInformationHeader.accountableHealthcareProfessional.healthcareProfessionalCareGiverHSAId</t>
-  </si>
-  <si>
-    <t>HSA-id för vårdgivare</t>
-  </si>
-  <si>
-    <t>HSA-id för vårdgivaren.
-Kardinalitet: Valfri.</t>
-  </si>
-  <si>
-    <t>SEEHDSLMAlertInformation.alertInformation.alertInformationHeader.legalAuthenticator</t>
-  </si>
-  <si>
-    <t>Signerande person</t>
-  </si>
-  <si>
-    <t>Information om vem som signerat informationen i dokumentet.
-Kardinalitet: Valfri.</t>
-  </si>
-  <si>
-    <t>SEEHDSLMAlertInformation.alertInformation.alertInformationHeader.legalAuthenticator.id</t>
-  </si>
-  <si>
-    <t>SEEHDSLMAlertInformation.alertInformation.alertInformationHeader.legalAuthenticator.extension</t>
-  </si>
-  <si>
-    <t>SEEHDSLMAlertInformation.alertInformation.alertInformationHeader.legalAuthenticator.modifierExtension</t>
-  </si>
-  <si>
-    <t>SEEHDSLMAlertInformation.alertInformation.alertInformationHeader.legalAuthenticator.signatureTime</t>
-  </si>
-  <si>
-    <t>Tidpunkt för signering</t>
-  </si>
-  <si>
-    <t>Tidpunkt för signering. Format: YYYYMMDDhhmmss.
-Kardinalitet: Obligatorisk.</t>
-  </si>
-  <si>
-    <t>SEEHDSLMAlertInformation.alertInformation.alertInformationHeader.legalAuthenticator.legalAuthenticatorHSAId</t>
-  </si>
-  <si>
-    <t>HSA-id för signerande</t>
-  </si>
-  <si>
-    <t>HSA-id för person som signerat dokumentet.
-Kardinalitet: Valfri.</t>
-  </si>
-  <si>
-    <t>SEEHDSLMAlertInformation.alertInformation.alertInformationHeader.legalAuthenticator.legalAuthenticatorName</t>
-  </si>
-  <si>
-    <t>Namn på signerande person</t>
-  </si>
-  <si>
-    <t>Namn i klartext för signerande person.
-Kardinalitet: Valfri.</t>
-  </si>
-  <si>
-    <t>SEEHDSLMAlertInformation.alertInformation.alertInformationHeader.approvedForPatient</t>
-  </si>
-  <si>
-    <t xml:space="preserve">boolean
-</t>
-  </si>
-  <si>
     <t>Godkänd för visning till patient</t>
   </si>
   <si>
-    <t>Anger om information får delas till patient.
-Kardinalitet: Obligatorisk.</t>
+    <t>Anger om information får delas till patient.</t>
   </si>
   <si>
     <t>SEEHDSLMAlertInformation.alertInformation.alertInformationHeader.careContactId</t>
@@ -640,8 +641,19 @@
     <t>Vårdkontakts-id</t>
   </si>
   <si>
-    <t>Identitet för den hälso- och sjukvårdskontakt som uppmärksamhetsinformationen gäller.
-Kardinalitet: Valfri.</t>
+    <t>Identitet för den hälso- och sjukvårdskontakt som uppmärksamhetsinformationen gäller.</t>
+  </si>
+  <si>
+    <t>SEEHDSLMAlertInformation.alertInformation.alertInformationHeader.nullified</t>
+  </si>
+  <si>
+    <t>Makulerad</t>
+  </si>
+  <si>
+    <t>SEEHDSLMAlertInformation.alertInformation.alertInformationHeader.nullifiedReason</t>
+  </si>
+  <si>
+    <t>Makuleringsorsak</t>
   </si>
   <si>
     <t>SEEHDSLMAlertInformation.alertInformation.alertInformationBody</t>
@@ -652,8 +664,7 @@
   <si>
     <t>AlertInformationBodyType — uppmärksamhetsinformationens informationsinnehåll.
 Exakt en av hypersensitivity, seriousDisease, treatment, communicableDisease,
-restrictionOfCare, unstructuredAlertInformation ska anges (XOR).
-Kardinalitet: Obligatorisk.</t>
+restrictionOfCare, unstructuredAlertInformation ska anges (XOR).</t>
   </si>
   <si>
     <t>SEEHDSLMAlertInformation.alertInformation.alertInformationBody.id</t>
@@ -674,7 +685,6 @@
     <t>Kod som anger vilken typ av uppmärksamhetssignal som avses.
 Bör tas från KV Uppmärksamhetstyp eller KV Informationstyp (OID 1.2.752.129.2.2.2.1).
 OID för KV Uppmärksamhetstyp saknas – använd KV Informationstyp som fallback.
-Kardinalitet: Obligatorisk.
 Regel 2 (NPÖ): För att uppmärksamhetssignaler ska skickas till NPÖ måste en av följande
 KV Informationstyp-koder anges: upp-ube, upp-ube-beh, upp-ube-lbe, upp-ube-kod, upp-uas,
 upp-uas-sjd, upp-vbe, upp-vbe-vbe, upp-arb, upp-arb-smf, upp-arb-smf-vag, upp-arb-smf-sjd,
@@ -686,7 +696,7 @@
     <t>SEEHDSLMAlertInformation.alertInformation.alertInformationBody.ascertainedDate</t>
   </si>
   <si>
-    <t xml:space="preserve">date
+    <t xml:space="preserve">https://fhir.inera.se/ig/ehds-tk/StructureDefinition/SEEHDSRivDate
 </t>
   </si>
   <si>
@@ -694,7 +704,7 @@
   </si>
   <si>
     <t>Datum då förhållandet som föranledde uppmärksamhetssignalen konstaterades.
-Kardinalitet: Valfri.</t>
+Format enligt XSD (DateType): ÅÅÅÅMMDD.</t>
   </si>
   <si>
     <t>SEEHDSLMAlertInformation.alertInformation.alertInformationBody.verifiedTime</t>
@@ -704,47 +714,21 @@
   </si>
   <si>
     <t>Tidpunkt då uppmärksamhetssignalen verifierades i det lokala systemet.
-Kardinalitet: Valfri.</t>
+Format enligt XSD (TimeStampType): ÅÅÅÅMMDDttmmss.</t>
   </si>
   <si>
     <t>SEEHDSLMAlertInformation.alertInformation.alertInformationBody.validityTimePeriod</t>
   </si>
   <si>
+    <t xml:space="preserve">https://fhir.inera.se/ig/ehds-tk/StructureDefinition/SEEHDSRivTimePeriodTypeHealthcondDescription2
+</t>
+  </si>
+  <si>
     <t>Giltighetstid</t>
   </si>
   <si>
     <t>Tidsintervallet inom vilket uppmärksamhetssignalen är giltig.
-Kardinalitet: Obligatorisk.</t>
-  </si>
-  <si>
-    <t>SEEHDSLMAlertInformation.alertInformation.alertInformationBody.validityTimePeriod.id</t>
-  </si>
-  <si>
-    <t>SEEHDSLMAlertInformation.alertInformation.alertInformationBody.validityTimePeriod.extension</t>
-  </si>
-  <si>
-    <t>SEEHDSLMAlertInformation.alertInformation.alertInformationBody.validityTimePeriod.modifierExtension</t>
-  </si>
-  <si>
-    <t>SEEHDSLMAlertInformation.alertInformation.alertInformationBody.validityTimePeriod.start</t>
-  </si>
-  <si>
-    <t>Startdatum för giltighet</t>
-  </si>
-  <si>
-    <t>Startdatum/tidpunkt för giltighetstiden. Format: YYYYMMDDhhmmss.
-Kardinalitet: Obligatorisk.</t>
-  </si>
-  <si>
-    <t>SEEHDSLMAlertInformation.alertInformation.alertInformationBody.validityTimePeriod.end</t>
-  </si>
-  <si>
-    <t>Slutdatum för giltighet</t>
-  </si>
-  <si>
-    <t>Slutdatum/tidpunkt för giltighetstiden. Format: YYYYMMDDhhmmss.
-Anges när man bedömer att uppmärksamhetssignalen har en känd sluttidpunkt.
-Kardinalitet: Valfri.</t>
+Enligt TKB i detta sammanhang: start 1..1.</t>
   </si>
   <si>
     <t>SEEHDSLMAlertInformation.alertInformation.alertInformationBody.alertInformationComment</t>
@@ -754,8 +738,7 @@
   </si>
   <si>
     <t>Kommentar av ansvarig hälso- och sjukvårdspersonal angående uppmärksamhetssignalen.
-Vid läkemedelsöverkänslighet kan kommentaren avse anamnes, reaktionsbeskrivning, möjliga agens.
-Kardinalitet: Valfri.</t>
+Vid läkemedelsöverkänslighet kan kommentaren avse anamnes, reaktionsbeskrivning, möjliga agens.</t>
   </si>
   <si>
     <t>SEEHDSLMAlertInformation.alertInformation.alertInformationBody.obsoleteTime</t>
@@ -765,7 +748,7 @@
   </si>
   <si>
     <t>Tidpunkt då uppmärksamhetssignalen registrerades som inaktuell i det lokala systemet.
-Kardinalitet: Valfri.</t>
+Format enligt XSD (TimeStampType): ÅÅÅÅMMDDttmmss.</t>
   </si>
   <si>
     <t>SEEHDSLMAlertInformation.alertInformation.alertInformationBody.obsoleteComment</t>
@@ -774,8 +757,7 @@
     <t>Kommentar till inaktivering</t>
   </si>
   <si>
-    <t>Information om varför uppmärksamhetssignalen gjorts inaktuell.
-Kardinalitet: Valfri.</t>
+    <t>Information om varför uppmärksamhetssignalen gjorts inaktuell.</t>
   </si>
   <si>
     <t>SEEHDSLMAlertInformation.alertInformation.alertInformationBody.hypersensitivity</t>
@@ -784,8 +766,7 @@
     <t>Överkänslighet (HyperSensitivityType)</t>
   </si>
   <si>
-    <t>XOR med seriousDisease, treatment, communicableDisease, restrictionOfCare, unstructuredAlertInformation.
-Kardinalitet: Valfri.</t>
+    <t>XOR med seriousDisease, treatment, communicableDisease, restrictionOfCare, unstructuredAlertInformation.</t>
   </si>
   <si>
     <t>SEEHDSLMAlertInformation.alertInformation.alertInformationBody.hypersensitivity.id</t>
@@ -804,8 +785,7 @@
   </si>
   <si>
     <t>Precisering av överkänslighetstyp (ICD10/SNOMED).
-T.ex. läkemedelsöverkänslighet, överkänslighet mot födoämne, djur, växt eller kemikalie.
-Kardinalitet: Valfri.</t>
+T.ex. läkemedelsöverkänslighet, överkänslighet mot födoämne, djur, växt eller kemikalie.</t>
   </si>
   <si>
     <t>SEEHDSLMAlertInformation.alertInformation.alertInformationBody.hypersensitivity.degreeOfSeverity</t>
@@ -814,8 +794,7 @@
     <t>Allvarlighetsgrad (CVType)</t>
   </si>
   <si>
-    <t>Bedömning av överkänslighetens allvarlighet. KV Allvarlighetsgrad (1.2.752.129.2.2.3.3).
-Kardinalitet: Valfri.</t>
+    <t>Bedömning av överkänslighetens allvarlighet. KV Allvarlighetsgrad (1.2.752.129.2.2.3.3).</t>
   </si>
   <si>
     <t>SEEHDSLMAlertInformation.alertInformation.alertInformationBody.hypersensitivity.degreeOfCertainty</t>
@@ -824,8 +803,7 @@
     <t>Visshet (CVType)</t>
   </si>
   <si>
-    <t>Visshetsgrad för överkänsligheten. KV Visshetsgrad (1.2.752.129.2.2.3.11).
-Kardinalitet: Valfri.</t>
+    <t>Visshetsgrad för överkänsligheten. KV Visshetsgrad (1.2.752.129.2.2.3.11).</t>
   </si>
   <si>
     <t>SEEHDSLMAlertInformation.alertInformation.alertInformationBody.hypersensitivity.pharmaceuticalHypersensitivity</t>
@@ -834,8 +812,7 @@
     <t>Läkemedelsöverkänslighet (PharmaceuticalHypersensitivityType)</t>
   </si>
   <si>
-    <t>Mer detaljerad information om läkemedelsöverkänslighet.
-Kardinalitet: Valfri.</t>
+    <t>Mer detaljerad information om läkemedelsöverkänslighet.</t>
   </si>
   <si>
     <t>SEEHDSLMAlertInformation.alertInformation.alertInformationBody.hypersensitivity.pharmaceuticalHypersensitivity.id</t>
@@ -856,10 +833,10 @@
     <t>Substans eller grupp av substanser som kan orsaka överkänslighetsreaktion.
 ATC-kod på minst treställig nivå ska anges vid livshotande/skadande allvarlighetsgrad.
 OID: 1.2.752.129.2.2.3.1.1.
-Kardinalitet: Valfri (villkorlig, se TKB).
 CVType-begränsningar (TKB): codeSystem är fast 1.2.752.129.2.2.3.1.1 (ATC).
 codeSystemName, codeSystemVersion och originalText är 0..0 (får ej anges).
-code och displayName är 1..1 (obligatoriska) när atcSubstance anges.</t>
+code och displayName är 1..1 (obligatoriska) när atcSubstance anges.
+Enligt TKB i detta sammanhang: code 1..1, codeSystem 1..1, codeSystemName 0..0, codeSystemVersion 0..0, displayName 1..1, originalText 0..0.</t>
   </si>
   <si>
     <t>SEEHDSLMAlertInformation.alertInformation.alertInformationBody.hypersensitivity.pharmaceuticalHypersensitivity.nonATCSubstance</t>
@@ -870,7 +847,6 @@
   <si>
     <t>Benämning på aktiv substans utan ATC-kod.
 Ska anges om atcSubstance saknas.
-Kardinalitet: Valfri.
 Villkor (TKB): nonATCSubstance och nonATCSubstanceComment ska BÅDA anges om atcSubstance saknas.</t>
   </si>
   <si>
@@ -882,7 +858,6 @@
   <si>
     <t>Förklaring till varför ATC-kod inte används.
 Ska anges om atcSubstance saknas.
-Kardinalitet: Valfri.
 Villkor (TKB): Ska anges om atcSubstance saknas (tillsammans med nonATCSubstance).</t>
   </si>
   <si>
@@ -892,8 +867,7 @@
     <t>Läkemedelsprodukt-id (CVType)</t>
   </si>
   <si>
-    <t>Identifierare för läkemedelsprodukt som kan orsaka överkänslighet. NPL-id (1.2.752.129.2.1.5.1).
-Kardinalitet: Valfri, lista.</t>
+    <t>Identifierare för läkemedelsprodukt som kan orsaka överkänslighet. NPL-id (1.2.752.129.2.1.5.1).</t>
   </si>
   <si>
     <t>SEEHDSLMAlertInformation.alertInformation.alertInformationBody.hypersensitivity.otherHypersensitivity</t>
@@ -902,8 +876,7 @@
     <t>Annan överkänslighet (OtherHypersensitivityType)</t>
   </si>
   <si>
-    <t>Mer detaljerad information om överkänslighet som ej är läkemedelsöverkänslighet.
-Kardinalitet: Valfri.</t>
+    <t>Mer detaljerad information om överkänslighet som ej är läkemedelsöverkänslighet.</t>
   </si>
   <si>
     <t>SEEHDSLMAlertInformation.alertInformation.alertInformationBody.hypersensitivity.otherHypersensitivity.id</t>
@@ -921,8 +894,7 @@
     <t>Agens</t>
   </si>
   <si>
-    <t>Text som beskriver det agens som bedöms kunna orsaka överkänslighetsreaktion.
-Kardinalitet: Valfri.</t>
+    <t>Text som beskriver det agens som bedöms kunna orsaka överkänslighetsreaktion.</t>
   </si>
   <si>
     <t>SEEHDSLMAlertInformation.alertInformation.alertInformationBody.hypersensitivity.otherHypersensitivity.hypersensitivityAgentCode</t>
@@ -932,8 +904,7 @@
   </si>
   <si>
     <t>Kod för det agens som bedöms kunna orsaka överkänslighetsreaktion.
-T.ex. LMK-kod (foderkänslighet) eller CAS-kod (kemikalie).
-Kardinalitet: Valfri.</t>
+T.ex. LMK-kod (foderkänslighet) eller CAS-kod (kemikalie).</t>
   </si>
   <si>
     <t>SEEHDSLMAlertInformation.alertInformation.alertInformationBody.seriousDisease</t>
@@ -942,8 +913,7 @@
     <t>Allvarlig sjukdom (SeriousDiseaseType)</t>
   </si>
   <si>
-    <t>XOR med hypersensitivity, treatment, communicableDisease, restrictionOfCare, unstructuredAlertInformation.
-Kardinalitet: Valfri.</t>
+    <t>XOR med hypersensitivity, treatment, communicableDisease, restrictionOfCare, unstructuredAlertInformation.</t>
   </si>
   <si>
     <t>SEEHDSLMAlertInformation.alertInformation.alertInformationBody.seriousDisease.id</t>
@@ -961,8 +931,7 @@
     <t>Sjukdomskod (CVType)</t>
   </si>
   <si>
-    <t>Allvarlig sjukdom som patienten har. ICD10/SNOMED rekommenderas.
-Kardinalitet: Obligatorisk.</t>
+    <t>Allvarlig sjukdom som patienten har. ICD10/SNOMED rekommenderas.</t>
   </si>
   <si>
     <t>SEEHDSLMAlertInformation.alertInformation.alertInformationBody.treatment</t>
@@ -971,8 +940,7 @@
     <t>Behandling (TreatmentType)</t>
   </si>
   <si>
-    <t>XOR med hypersensitivity, seriousDisease, communicableDisease, restrictionOfCare, unstructuredAlertInformation.
-Kardinalitet: Valfri.</t>
+    <t>XOR med hypersensitivity, seriousDisease, communicableDisease, restrictionOfCare, unstructuredAlertInformation.</t>
   </si>
   <si>
     <t>SEEHDSLMAlertInformation.alertInformation.alertInformationBody.treatment.id</t>
@@ -990,8 +958,7 @@
     <t>Behandlingsbeskrivning</t>
   </si>
   <si>
-    <t>Beskrivning av allvarlig behandling som patienten genomgår.
-Kardinalitet: Obligatorisk.</t>
+    <t>Beskrivning av allvarlig behandling som patienten genomgår.</t>
   </si>
   <si>
     <t>SEEHDSLMAlertInformation.alertInformation.alertInformationBody.treatment.treatmentCode</t>
@@ -1000,8 +967,7 @@
     <t>Behandlingskod (CVType)</t>
   </si>
   <si>
-    <t>Preciserad uppgift om behandlingen. KVÅ-kod (1.2.752.116.1.3.2.1.4) rekommenderas.
-Kardinalitet: Valfri.</t>
+    <t>Preciserad uppgift om behandlingen. KVÅ-kod (1.2.752.116.1.3.2.1.4) rekommenderas.</t>
   </si>
   <si>
     <t>SEEHDSLMAlertInformation.alertInformation.alertInformationBody.treatment.pharmaceuticalTreatment</t>
@@ -1010,8 +976,7 @@
     <t>Läkemedel vid behandling (CVType)</t>
   </si>
   <si>
-    <t>Läkemedel som används vid uppmärksammad behandling. ATC-kod (1.2.752.129.2.2.3.1.1) rekommenderas.
-Kardinalitet: Valfri, lista.</t>
+    <t>Läkemedel som används vid uppmärksammad behandling. ATC-kod (1.2.752.129.2.2.3.1.1) rekommenderas.</t>
   </si>
   <si>
     <t>SEEHDSLMAlertInformation.alertInformation.alertInformationBody.communicableDisease</t>
@@ -1020,8 +985,7 @@
     <t>Smittsam sjukdom (CommunicableDiseaseType)</t>
   </si>
   <si>
-    <t>XOR med hypersensitivity, seriousDisease, treatment, restrictionOfCare, unstructuredAlertInformation.
-Kardinalitet: Valfri.</t>
+    <t>XOR med hypersensitivity, seriousDisease, treatment, restrictionOfCare, unstructuredAlertInformation.</t>
   </si>
   <si>
     <t>SEEHDSLMAlertInformation.alertInformation.alertInformationBody.communicableDisease.id</t>
@@ -1039,8 +1003,7 @@
     <t>Smittsam sjukdomskod (CVType)</t>
   </si>
   <si>
-    <t>Kod för smittsam sjukdom. ICD10 rekommenderas.
-Kardinalitet: Obligatorisk.</t>
+    <t>Kod för smittsam sjukdom. ICD10 rekommenderas.</t>
   </si>
   <si>
     <t>SEEHDSLMAlertInformation.alertInformation.alertInformationBody.communicableDisease.routeOfTransmission</t>
@@ -1049,8 +1012,7 @@
     <t>Smittväg (CVType)</t>
   </si>
   <si>
-    <t>Kod för hur sjukdomen smittar. KV Smittväg.
-Kardinalitet: Valfri.</t>
+    <t>Kod för hur sjukdomen smittar. KV Smittväg.</t>
   </si>
   <si>
     <t>SEEHDSLMAlertInformation.alertInformation.alertInformationBody.restrictionOfCare</t>
@@ -1059,8 +1021,7 @@
     <t>Vårdbegränsning (RestrictionOfCareType)</t>
   </si>
   <si>
-    <t>XOR med hypersensitivity, seriousDisease, treatment, communicableDisease, unstructuredAlertInformation.
-Kardinalitet: Valfri.</t>
+    <t>XOR med hypersensitivity, seriousDisease, treatment, communicableDisease, unstructuredAlertInformation.</t>
   </si>
   <si>
     <t>SEEHDSLMAlertInformation.alertInformation.alertInformationBody.restrictionOfCare.id</t>
@@ -1078,8 +1039,7 @@
     <t>Kommentar om vårdbegränsning</t>
   </si>
   <si>
-    <t>Information om uppmärksammat förhållande som inte avser överkänslighet, sjukdom eller behandling.
-Kardinalitet: Obligatorisk.</t>
+    <t>Information om uppmärksammat förhållande som inte avser överkänslighet, sjukdom eller behandling.</t>
   </si>
   <si>
     <t>SEEHDSLMAlertInformation.alertInformation.alertInformationBody.unstructuredAlertInformation</t>
@@ -1089,8 +1049,7 @@
   </si>
   <si>
     <t>XOR med hypersensitivity, seriousDisease, treatment, communicableDisease, restrictionOfCare.
-Används för tidigare varningsinformation som inte följer NPÖ-strukturen.
-Kardinalitet: Valfri.</t>
+Används för tidigare varningsinformation som inte följer NPÖ-strukturen.</t>
   </si>
   <si>
     <t>SEEHDSLMAlertInformation.alertInformation.alertInformationBody.unstructuredAlertInformation.id</t>
@@ -1108,8 +1067,7 @@
     <t>Rubrik för historisk varning</t>
   </si>
   <si>
-    <t>Beskrivande rubrik för tidigare utfärdad varning.
-Kardinalitet: Obligatorisk.</t>
+    <t>Beskrivande rubrik för tidigare utfärdad varning.</t>
   </si>
   <si>
     <t>SEEHDSLMAlertInformation.alertInformation.alertInformationBody.unstructuredAlertInformation.unstructuredAlertInformationContent</t>
@@ -1118,8 +1076,7 @@
     <t>Innehåll för historisk varning</t>
   </si>
   <si>
-    <t>Beskrivning av vad varningen gäller samt viss administrativ information.
-Kardinalitet: Obligatorisk.</t>
+    <t>Beskrivning av vad varningen gäller samt viss administrativ information.</t>
   </si>
   <si>
     <t>SEEHDSLMAlertInformation.alertInformation.alertInformationBody.relatedAlertInformation</t>
@@ -1128,8 +1085,7 @@
     <t>Relaterad uppmärksamhetssignal (RelatedAlertInformationType)</t>
   </si>
   <si>
-    <t>Information om samband med andra uppmärksamhetssignaler.
-Kardinalitet: Valfri, lista.</t>
+    <t>Information om samband med andra uppmärksamhetssignaler.</t>
   </si>
   <si>
     <t>SEEHDSLMAlertInformation.alertInformation.alertInformationBody.relatedAlertInformation.id</t>
@@ -1147,8 +1103,7 @@
     <t>Typ av samband (CVType)</t>
   </si>
   <si>
-    <t>Typ av samband. KV Samband (1.2.752.129.2.2.2.4).
-Kardinalitet: Obligatorisk.</t>
+    <t>Typ av samband. KV Samband (1.2.752.129.2.2.2.4).</t>
   </si>
   <si>
     <t>SEEHDSLMAlertInformation.alertInformation.alertInformationBody.relatedAlertInformation.relationComment</t>
@@ -1157,8 +1112,7 @@
     <t>Kommentar till samband</t>
   </si>
   <si>
-    <t>Kommentar till det aktuella sambandet.
-Kardinalitet: Valfri.</t>
+    <t>Kommentar till det aktuella sambandet.</t>
   </si>
   <si>
     <t>SEEHDSLMAlertInformation.alertInformation.alertInformationBody.relatedAlertInformation.documentId</t>
@@ -1167,8 +1121,7 @@
     <t>Relaterad dokumentidentitet</t>
   </si>
   <si>
-    <t>Lokalt unik identitet för relaterad uppmärksamhetssignal.
-Kardinalitet: Obligatorisk, lista (minst en).</t>
+    <t>Lokalt unik identitet för relaterad uppmärksamhetssignal.</t>
   </si>
   <si>
     <t>SEEHDSLMAlertInformation.result</t>
@@ -1177,8 +1130,7 @@
     <t>Resultat</t>
   </si>
   <si>
-    <t>Innehåller information om begäran gick bra eller ej.
-Kardinalitet: Obligatorisk.</t>
+    <t>Innehåller information om begäran gick bra eller ej.</t>
   </si>
   <si>
     <t>SEEHDSLMAlertInformation.result.id</t>
@@ -1193,15 +1145,11 @@
     <t>SEEHDSLMAlertInformation.result.resultCode</t>
   </si>
   <si>
-    <t xml:space="preserve">code
-</t>
-  </si>
-  <si>
     <t>Resultatkod</t>
   </si>
   <si>
     <t>Kan endast vara OK, INFO eller ERROR.
-Kardinalitet: Obligatorisk.</t>
+Tillåtna värden enligt XSD: OK, ERROR, INFO.</t>
   </si>
   <si>
     <t>SEEHDSLMAlertInformation.result.errorCode</t>
@@ -1211,27 +1159,25 @@
   </si>
   <si>
     <t>Sätts endast om resultCode är ERROR. Tillåtna värden: INVALID_REQUEST.
-Kardinalitet: Valfri.</t>
-  </si>
-  <si>
-    <t>SEEHDSLMAlertInformation.result.subcode</t>
+Tillåtna värden enligt XSD: INVALID_REQUEST.</t>
+  </si>
+  <si>
+    <t>SEEHDSLMAlertInformation.result.logId</t>
+  </si>
+  <si>
+    <t>Log-id</t>
+  </si>
+  <si>
+    <t>En UUID som kan användas vid felanmälan för att spåra felet.</t>
+  </si>
+  <si>
+    <t>SEEHDSLMAlertInformation.result.subCode</t>
   </si>
   <si>
     <t>Subkod</t>
   </si>
   <si>
-    <t>Inga subkoder specificerade.
-Kardinalitet: Valfri.</t>
-  </si>
-  <si>
-    <t>SEEHDSLMAlertInformation.result.logId</t>
-  </si>
-  <si>
-    <t>Log-id</t>
-  </si>
-  <si>
-    <t>En UUID som kan användas vid felanmälan för att spåra felet.
-Kardinalitet: Obligatorisk.</t>
+    <t>Inga subkoder specificerade.</t>
   </si>
   <si>
     <t>SEEHDSLMAlertInformation.result.message</t>
@@ -1240,8 +1186,7 @@
     <t>Meddelande</t>
   </si>
   <si>
-    <t>En beskrivande text som kan visas för användaren.
-Kardinalitet: Valfri.</t>
+    <t>En beskrivande text som kan visas för användaren.</t>
   </si>
 </sst>
 </file>
@@ -1543,7 +1488,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AJ124"/>
+  <dimension ref="A1:AJ123"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="122.0859375" customWidth="true" bestFit="true"/>
@@ -1556,7 +1501,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="15.140625" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="80.8125" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -2633,13 +2578,13 @@
         <v>72</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>84</v>
+        <v>113</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="N11" s="2"/>
       <c r="O11" s="2"/>
@@ -2707,10 +2652,10 @@
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -2733,7 +2678,7 @@
         <v>72</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="L12" t="s" s="2">
         <v>117</v>
@@ -2790,7 +2735,7 @@
         <v>72</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>83</v>
@@ -2818,10 +2763,10 @@
       </c>
       <c r="E13" s="2"/>
       <c r="F13" t="s" s="2">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="G13" t="s" s="2">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="H13" t="s" s="2">
         <v>72</v>
@@ -2833,7 +2778,7 @@
         <v>72</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="L13" t="s" s="2">
         <v>120</v>
@@ -2893,10 +2838,10 @@
         <v>119</v>
       </c>
       <c r="AG13" t="s" s="2">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="AH13" t="s" s="2">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="AI13" t="s" s="2">
         <v>72</v>
@@ -2918,10 +2863,10 @@
       </c>
       <c r="E14" s="2"/>
       <c r="F14" t="s" s="2">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="G14" t="s" s="2">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="H14" t="s" s="2">
         <v>72</v>
@@ -2933,13 +2878,13 @@
         <v>72</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>78</v>
+        <v>123</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="N14" s="2"/>
       <c r="O14" s="2"/>
@@ -2993,24 +2938,24 @@
         <v>122</v>
       </c>
       <c r="AG14" t="s" s="2">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="AH14" t="s" s="2">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="AI14" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AJ14" t="s" s="2">
-        <v>81</v>
+        <v>72</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -3018,7 +2963,7 @@
       </c>
       <c r="E15" s="2"/>
       <c r="F15" t="s" s="2">
-        <v>73</v>
+        <v>83</v>
       </c>
       <c r="G15" t="s" s="2">
         <v>83</v>
@@ -3033,13 +2978,13 @@
         <v>72</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>84</v>
+        <v>127</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>85</v>
+        <v>128</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>86</v>
+        <v>129</v>
       </c>
       <c r="N15" s="2"/>
       <c r="O15" s="2"/>
@@ -3090,10 +3035,10 @@
         <v>72</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>87</v>
+        <v>126</v>
       </c>
       <c r="AG15" t="s" s="2">
-        <v>73</v>
+        <v>83</v>
       </c>
       <c r="AH15" t="s" s="2">
         <v>83</v>
@@ -3107,21 +3052,21 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
-        <v>89</v>
+        <v>72</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
-        <v>73</v>
+        <v>83</v>
       </c>
       <c r="G16" t="s" s="2">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="H16" t="s" s="2">
         <v>72</v>
@@ -3133,17 +3078,15 @@
         <v>72</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>91</v>
+        <v>131</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="N16" t="s" s="2">
-        <v>93</v>
-      </c>
+        <v>132</v>
+      </c>
+      <c r="N16" s="2"/>
       <c r="O16" s="2"/>
       <c r="P16" t="s" s="2">
         <v>72</v>
@@ -3180,75 +3123,71 @@
         <v>72</v>
       </c>
       <c r="AB16" t="s" s="2">
-        <v>94</v>
+        <v>72</v>
       </c>
       <c r="AC16" t="s" s="2">
-        <v>95</v>
+        <v>72</v>
       </c>
       <c r="AD16" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AE16" t="s" s="2">
-        <v>96</v>
+        <v>72</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>97</v>
+        <v>130</v>
       </c>
       <c r="AG16" t="s" s="2">
-        <v>73</v>
+        <v>83</v>
       </c>
       <c r="AH16" t="s" s="2">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="AI16" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AJ16" t="s" s="2">
-        <v>98</v>
+        <v>81</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
-        <v>100</v>
+        <v>72</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
         <v>73</v>
       </c>
       <c r="G17" t="s" s="2">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="H17" t="s" s="2">
         <v>72</v>
       </c>
       <c r="I17" t="s" s="2">
-        <v>101</v>
+        <v>72</v>
       </c>
       <c r="J17" t="s" s="2">
-        <v>101</v>
+        <v>72</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>102</v>
+        <v>85</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="N17" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="O17" t="s" s="2">
-        <v>104</v>
-      </c>
+        <v>86</v>
+      </c>
+      <c r="N17" s="2"/>
+      <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
         <v>72</v>
       </c>
@@ -3296,38 +3235,38 @@
         <v>72</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>105</v>
+        <v>87</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AH17" t="s" s="2">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="AI17" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AJ17" t="s" s="2">
-        <v>98</v>
+        <v>72</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>128</v>
+        <v>134</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>128</v>
+        <v>134</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
-        <v>72</v>
+        <v>89</v>
       </c>
       <c r="E18" s="2"/>
       <c r="F18" t="s" s="2">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="G18" t="s" s="2">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="H18" t="s" s="2">
         <v>72</v>
@@ -3339,15 +3278,17 @@
         <v>72</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>129</v>
+        <v>90</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>130</v>
+        <v>91</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>131</v>
-      </c>
-      <c r="N18" s="2"/>
+        <v>92</v>
+      </c>
+      <c r="N18" t="s" s="2">
+        <v>93</v>
+      </c>
       <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
         <v>72</v>
@@ -3384,71 +3325,75 @@
         <v>72</v>
       </c>
       <c r="AB18" t="s" s="2">
-        <v>72</v>
+        <v>94</v>
       </c>
       <c r="AC18" t="s" s="2">
-        <v>72</v>
+        <v>95</v>
       </c>
       <c r="AD18" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AE18" t="s" s="2">
-        <v>72</v>
+        <v>96</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>128</v>
+        <v>97</v>
       </c>
       <c r="AG18" t="s" s="2">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="AH18" t="s" s="2">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="AI18" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AJ18" t="s" s="2">
-        <v>72</v>
+        <v>98</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
-        <v>72</v>
+        <v>100</v>
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
         <v>73</v>
       </c>
       <c r="G19" t="s" s="2">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="H19" t="s" s="2">
         <v>72</v>
       </c>
       <c r="I19" t="s" s="2">
-        <v>72</v>
+        <v>101</v>
       </c>
       <c r="J19" t="s" s="2">
-        <v>72</v>
+        <v>101</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>116</v>
+        <v>90</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>133</v>
+        <v>102</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>134</v>
-      </c>
-      <c r="N19" s="2"/>
-      <c r="O19" s="2"/>
+        <v>103</v>
+      </c>
+      <c r="N19" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="O19" t="s" s="2">
+        <v>104</v>
+      </c>
       <c r="P19" t="s" s="2">
         <v>72</v>
       </c>
@@ -3496,27 +3441,27 @@
         <v>72</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>132</v>
+        <v>105</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AH19" t="s" s="2">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="AI19" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AJ19" t="s" s="2">
-        <v>72</v>
+        <v>98</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -3524,7 +3469,7 @@
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
-        <v>73</v>
+        <v>83</v>
       </c>
       <c r="G20" t="s" s="2">
         <v>83</v>
@@ -3539,13 +3484,13 @@
         <v>72</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>84</v>
+        <v>123</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
@@ -3596,10 +3541,10 @@
         <v>72</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="AG20" t="s" s="2">
-        <v>73</v>
+        <v>83</v>
       </c>
       <c r="AH20" t="s" s="2">
         <v>83</v>
@@ -3613,10 +3558,10 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -3639,7 +3584,7 @@
         <v>72</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>139</v>
+        <v>113</v>
       </c>
       <c r="L21" t="s" s="2">
         <v>140</v>
@@ -3696,7 +3641,7 @@
         <v>72</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>73</v>
@@ -3739,7 +3684,7 @@
         <v>72</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>78</v>
+        <v>113</v>
       </c>
       <c r="L22" t="s" s="2">
         <v>143</v>
@@ -3808,7 +3753,7 @@
         <v>72</v>
       </c>
       <c r="AJ22" t="s" s="2">
-        <v>81</v>
+        <v>72</v>
       </c>
     </row>
     <row r="23">
@@ -3839,13 +3784,13 @@
         <v>72</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>84</v>
+        <v>146</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>85</v>
+        <v>147</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>86</v>
+        <v>148</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" s="2"/>
@@ -3896,7 +3841,7 @@
         <v>72</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>87</v>
+        <v>145</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>73</v>
@@ -3913,21 +3858,21 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
-        <v>89</v>
+        <v>72</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
         <v>73</v>
       </c>
       <c r="G24" t="s" s="2">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="H24" t="s" s="2">
         <v>72</v>
@@ -3939,17 +3884,15 @@
         <v>72</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>91</v>
+        <v>150</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="N24" t="s" s="2">
-        <v>93</v>
-      </c>
+        <v>151</v>
+      </c>
+      <c r="N24" s="2"/>
       <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
         <v>72</v>
@@ -3986,75 +3929,71 @@
         <v>72</v>
       </c>
       <c r="AB24" t="s" s="2">
-        <v>94</v>
+        <v>72</v>
       </c>
       <c r="AC24" t="s" s="2">
-        <v>95</v>
+        <v>72</v>
       </c>
       <c r="AD24" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AE24" t="s" s="2">
-        <v>96</v>
+        <v>72</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>97</v>
+        <v>149</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AH24" t="s" s="2">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="AI24" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>98</v>
+        <v>81</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
-        <v>100</v>
+        <v>72</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
         <v>73</v>
       </c>
       <c r="G25" t="s" s="2">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="H25" t="s" s="2">
         <v>72</v>
       </c>
       <c r="I25" t="s" s="2">
-        <v>101</v>
+        <v>72</v>
       </c>
       <c r="J25" t="s" s="2">
-        <v>101</v>
+        <v>72</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>102</v>
+        <v>85</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="N25" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="O25" t="s" s="2">
-        <v>104</v>
-      </c>
+        <v>86</v>
+      </c>
+      <c r="N25" s="2"/>
+      <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
         <v>72</v>
       </c>
@@ -4102,38 +4041,38 @@
         <v>72</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>105</v>
+        <v>87</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AH25" t="s" s="2">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="AI25" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>98</v>
+        <v>72</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>148</v>
+        <v>153</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>148</v>
+        <v>153</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
-        <v>72</v>
+        <v>89</v>
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="G26" t="s" s="2">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="H26" t="s" s="2">
         <v>72</v>
@@ -4145,15 +4084,17 @@
         <v>72</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>116</v>
+        <v>90</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>149</v>
+        <v>91</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>150</v>
-      </c>
-      <c r="N26" s="2"/>
+        <v>92</v>
+      </c>
+      <c r="N26" t="s" s="2">
+        <v>93</v>
+      </c>
       <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
         <v>72</v>
@@ -4190,71 +4131,75 @@
         <v>72</v>
       </c>
       <c r="AB26" t="s" s="2">
-        <v>72</v>
+        <v>94</v>
       </c>
       <c r="AC26" t="s" s="2">
-        <v>72</v>
+        <v>95</v>
       </c>
       <c r="AD26" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AE26" t="s" s="2">
-        <v>72</v>
+        <v>96</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>148</v>
+        <v>97</v>
       </c>
       <c r="AG26" t="s" s="2">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="AH26" t="s" s="2">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="AI26" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AJ26" t="s" s="2">
-        <v>72</v>
+        <v>98</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
-        <v>72</v>
+        <v>100</v>
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="G27" t="s" s="2">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="H27" t="s" s="2">
         <v>72</v>
       </c>
       <c r="I27" t="s" s="2">
-        <v>72</v>
+        <v>101</v>
       </c>
       <c r="J27" t="s" s="2">
-        <v>72</v>
+        <v>101</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>152</v>
+        <v>102</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>153</v>
-      </c>
-      <c r="N27" s="2"/>
-      <c r="O27" s="2"/>
+        <v>103</v>
+      </c>
+      <c r="N27" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="O27" t="s" s="2">
+        <v>104</v>
+      </c>
       <c r="P27" t="s" s="2">
         <v>72</v>
       </c>
@@ -4302,27 +4247,27 @@
         <v>72</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>151</v>
+        <v>105</v>
       </c>
       <c r="AG27" t="s" s="2">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="AH27" t="s" s="2">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="AI27" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AJ27" t="s" s="2">
-        <v>72</v>
+        <v>98</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -4330,7 +4275,7 @@
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
-        <v>73</v>
+        <v>83</v>
       </c>
       <c r="G28" t="s" s="2">
         <v>83</v>
@@ -4345,13 +4290,13 @@
         <v>72</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>84</v>
+        <v>113</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" s="2"/>
@@ -4402,10 +4347,10 @@
         <v>72</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="AG28" t="s" s="2">
-        <v>73</v>
+        <v>83</v>
       </c>
       <c r="AH28" t="s" s="2">
         <v>83</v>
@@ -4419,10 +4364,10 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -4430,7 +4375,7 @@
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
-        <v>73</v>
+        <v>83</v>
       </c>
       <c r="G29" t="s" s="2">
         <v>83</v>
@@ -4445,13 +4390,13 @@
         <v>72</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>84</v>
+        <v>113</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="N29" s="2"/>
       <c r="O29" s="2"/>
@@ -4502,10 +4447,10 @@
         <v>72</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="AG29" t="s" s="2">
-        <v>73</v>
+        <v>83</v>
       </c>
       <c r="AH29" t="s" s="2">
         <v>83</v>
@@ -4519,10 +4464,10 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -4545,13 +4490,13 @@
         <v>72</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>84</v>
+        <v>113</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" s="2"/>
@@ -4602,7 +4547,7 @@
         <v>72</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>73</v>
@@ -4619,10 +4564,10 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -4645,13 +4590,13 @@
         <v>72</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>84</v>
+        <v>113</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
@@ -4702,7 +4647,7 @@
         <v>72</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>73</v>
@@ -4719,10 +4664,10 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -4745,13 +4690,13 @@
         <v>72</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
@@ -4802,7 +4747,7 @@
         <v>72</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>73</v>
@@ -4819,10 +4764,10 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -4845,13 +4790,13 @@
         <v>72</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
@@ -4902,7 +4847,7 @@
         <v>72</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>73</v>
@@ -4919,10 +4864,10 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -4945,13 +4890,13 @@
         <v>72</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>78</v>
+        <v>113</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
@@ -5002,7 +4947,7 @@
         <v>72</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>73</v>
@@ -5014,15 +4959,15 @@
         <v>72</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>81</v>
+        <v>72</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5045,13 +4990,13 @@
         <v>72</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>84</v>
+        <v>113</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>85</v>
+        <v>177</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>86</v>
+        <v>178</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
@@ -5102,7 +5047,7 @@
         <v>72</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>87</v>
+        <v>176</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>73</v>
@@ -5119,21 +5064,21 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
-        <v>89</v>
+        <v>72</v>
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
         <v>73</v>
       </c>
       <c r="G36" t="s" s="2">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="H36" t="s" s="2">
         <v>72</v>
@@ -5145,17 +5090,15 @@
         <v>72</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>91</v>
+        <v>180</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="N36" t="s" s="2">
-        <v>93</v>
-      </c>
+        <v>181</v>
+      </c>
+      <c r="N36" s="2"/>
       <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
         <v>72</v>
@@ -5192,75 +5135,71 @@
         <v>72</v>
       </c>
       <c r="AB36" t="s" s="2">
-        <v>94</v>
+        <v>72</v>
       </c>
       <c r="AC36" t="s" s="2">
-        <v>95</v>
+        <v>72</v>
       </c>
       <c r="AD36" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AE36" t="s" s="2">
-        <v>96</v>
+        <v>72</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>97</v>
+        <v>179</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AH36" t="s" s="2">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="AI36" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AJ36" t="s" s="2">
-        <v>98</v>
+        <v>81</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>177</v>
+        <v>182</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>177</v>
+        <v>182</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
-        <v>100</v>
+        <v>72</v>
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
         <v>73</v>
       </c>
       <c r="G37" t="s" s="2">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="H37" t="s" s="2">
         <v>72</v>
       </c>
       <c r="I37" t="s" s="2">
-        <v>101</v>
+        <v>72</v>
       </c>
       <c r="J37" t="s" s="2">
-        <v>101</v>
+        <v>72</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>102</v>
+        <v>85</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="N37" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="O37" t="s" s="2">
-        <v>104</v>
-      </c>
+        <v>86</v>
+      </c>
+      <c r="N37" s="2"/>
+      <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
         <v>72</v>
       </c>
@@ -5308,38 +5247,38 @@
         <v>72</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>105</v>
+        <v>87</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AH37" t="s" s="2">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="AI37" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AJ37" t="s" s="2">
-        <v>98</v>
+        <v>72</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>178</v>
+        <v>183</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>178</v>
+        <v>183</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
-        <v>72</v>
+        <v>89</v>
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="G38" t="s" s="2">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="H38" t="s" s="2">
         <v>72</v>
@@ -5351,15 +5290,17 @@
         <v>72</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>129</v>
+        <v>90</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>179</v>
+        <v>91</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>180</v>
-      </c>
-      <c r="N38" s="2"/>
+        <v>92</v>
+      </c>
+      <c r="N38" t="s" s="2">
+        <v>93</v>
+      </c>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
         <v>72</v>
@@ -5396,71 +5337,75 @@
         <v>72</v>
       </c>
       <c r="AB38" t="s" s="2">
-        <v>72</v>
+        <v>94</v>
       </c>
       <c r="AC38" t="s" s="2">
-        <v>72</v>
+        <v>95</v>
       </c>
       <c r="AD38" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AE38" t="s" s="2">
-        <v>72</v>
+        <v>96</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>178</v>
+        <v>97</v>
       </c>
       <c r="AG38" t="s" s="2">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="AH38" t="s" s="2">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="AI38" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AJ38" t="s" s="2">
-        <v>72</v>
+        <v>98</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
-        <v>72</v>
+        <v>100</v>
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
         <v>73</v>
       </c>
       <c r="G39" t="s" s="2">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="H39" t="s" s="2">
         <v>72</v>
       </c>
       <c r="I39" t="s" s="2">
-        <v>72</v>
+        <v>101</v>
       </c>
       <c r="J39" t="s" s="2">
-        <v>72</v>
+        <v>101</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>116</v>
+        <v>90</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>182</v>
+        <v>102</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>183</v>
-      </c>
-      <c r="N39" s="2"/>
-      <c r="O39" s="2"/>
+        <v>103</v>
+      </c>
+      <c r="N39" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="O39" t="s" s="2">
+        <v>104</v>
+      </c>
       <c r="P39" t="s" s="2">
         <v>72</v>
       </c>
@@ -5508,27 +5453,27 @@
         <v>72</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>181</v>
+        <v>105</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AH39" t="s" s="2">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="AI39" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>72</v>
+        <v>98</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -5536,7 +5481,7 @@
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
-        <v>73</v>
+        <v>83</v>
       </c>
       <c r="G40" t="s" s="2">
         <v>83</v>
@@ -5551,13 +5496,13 @@
         <v>72</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>84</v>
+        <v>123</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -5608,10 +5553,10 @@
         <v>72</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="AG40" t="s" s="2">
-        <v>73</v>
+        <v>83</v>
       </c>
       <c r="AH40" t="s" s="2">
         <v>83</v>
@@ -5625,10 +5570,10 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -5636,7 +5581,7 @@
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="G41" t="s" s="2">
         <v>83</v>
@@ -5651,7 +5596,7 @@
         <v>72</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>188</v>
+        <v>113</v>
       </c>
       <c r="L41" t="s" s="2">
         <v>189</v>
@@ -5708,10 +5653,10 @@
         <v>72</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="AG41" t="s" s="2">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="AH41" t="s" s="2">
         <v>83</v>
@@ -5751,7 +5696,7 @@
         <v>72</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>84</v>
+        <v>113</v>
       </c>
       <c r="L42" t="s" s="2">
         <v>192</v>
@@ -5851,13 +5796,13 @@
         <v>72</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>78</v>
+        <v>195</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" s="2"/>
@@ -5920,15 +5865,15 @@
         <v>72</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>81</v>
+        <v>72</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -5951,13 +5896,13 @@
         <v>72</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>84</v>
+        <v>113</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>85</v>
+        <v>199</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>86</v>
+        <v>200</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" s="2"/>
@@ -6008,7 +5953,7 @@
         <v>72</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>87</v>
+        <v>198</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>73</v>
@@ -6025,21 +5970,21 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
-        <v>89</v>
+        <v>72</v>
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
         <v>73</v>
       </c>
       <c r="G45" t="s" s="2">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="H45" t="s" s="2">
         <v>72</v>
@@ -6051,17 +5996,15 @@
         <v>72</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>90</v>
+        <v>195</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>91</v>
+        <v>202</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="N45" t="s" s="2">
-        <v>93</v>
-      </c>
+        <v>121</v>
+      </c>
+      <c r="N45" s="2"/>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
         <v>72</v>
@@ -6098,75 +6041,71 @@
         <v>72</v>
       </c>
       <c r="AB45" t="s" s="2">
-        <v>94</v>
+        <v>72</v>
       </c>
       <c r="AC45" t="s" s="2">
-        <v>95</v>
+        <v>72</v>
       </c>
       <c r="AD45" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AE45" t="s" s="2">
-        <v>96</v>
+        <v>72</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>97</v>
+        <v>201</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AH45" t="s" s="2">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="AI45" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>98</v>
+        <v>72</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
-        <v>100</v>
+        <v>72</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
         <v>73</v>
       </c>
       <c r="G46" t="s" s="2">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="H46" t="s" s="2">
         <v>72</v>
       </c>
       <c r="I46" t="s" s="2">
-        <v>101</v>
+        <v>72</v>
       </c>
       <c r="J46" t="s" s="2">
-        <v>101</v>
+        <v>72</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>90</v>
+        <v>113</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>102</v>
+        <v>204</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="N46" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="O46" t="s" s="2">
-        <v>104</v>
-      </c>
+        <v>121</v>
+      </c>
+      <c r="N46" s="2"/>
+      <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
         <v>72</v>
       </c>
@@ -6214,27 +6153,27 @@
         <v>72</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>105</v>
+        <v>203</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AH46" t="s" s="2">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="AI46" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>98</v>
+        <v>72</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>200</v>
+        <v>205</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>200</v>
+        <v>205</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -6257,13 +6196,13 @@
         <v>72</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>139</v>
+        <v>78</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>201</v>
+        <v>206</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>202</v>
+        <v>207</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" s="2"/>
@@ -6314,7 +6253,7 @@
         <v>72</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>200</v>
+        <v>205</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>83</v>
@@ -6326,15 +6265,15 @@
         <v>72</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>72</v>
+        <v>81</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>203</v>
+        <v>208</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>203</v>
+        <v>208</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -6357,13 +6296,13 @@
         <v>72</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>204</v>
+        <v>84</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>205</v>
+        <v>85</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>206</v>
+        <v>86</v>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" s="2"/>
@@ -6414,7 +6353,7 @@
         <v>72</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>203</v>
+        <v>87</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>73</v>
@@ -6431,21 +6370,21 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
-        <v>72</v>
+        <v>89</v>
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
         <v>73</v>
       </c>
       <c r="G49" t="s" s="2">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="H49" t="s" s="2">
         <v>72</v>
@@ -6457,15 +6396,17 @@
         <v>72</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>129</v>
+        <v>90</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>208</v>
+        <v>91</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>209</v>
-      </c>
-      <c r="N49" s="2"/>
+        <v>92</v>
+      </c>
+      <c r="N49" t="s" s="2">
+        <v>93</v>
+      </c>
       <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
         <v>72</v>
@@ -6502,31 +6443,31 @@
         <v>72</v>
       </c>
       <c r="AB49" t="s" s="2">
-        <v>72</v>
+        <v>94</v>
       </c>
       <c r="AC49" t="s" s="2">
-        <v>72</v>
+        <v>95</v>
       </c>
       <c r="AD49" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AE49" t="s" s="2">
-        <v>72</v>
+        <v>96</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>207</v>
+        <v>97</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AH49" t="s" s="2">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="AI49" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>72</v>
+        <v>98</v>
       </c>
     </row>
     <row r="50">
@@ -6538,35 +6479,39 @@
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
-        <v>72</v>
+        <v>100</v>
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="G50" t="s" s="2">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="H50" t="s" s="2">
         <v>72</v>
       </c>
       <c r="I50" t="s" s="2">
-        <v>72</v>
+        <v>101</v>
       </c>
       <c r="J50" t="s" s="2">
-        <v>72</v>
+        <v>101</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>211</v>
+        <v>102</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>212</v>
-      </c>
-      <c r="N50" s="2"/>
-      <c r="O50" s="2"/>
+        <v>103</v>
+      </c>
+      <c r="N50" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="O50" t="s" s="2">
+        <v>104</v>
+      </c>
       <c r="P50" t="s" s="2">
         <v>72</v>
       </c>
@@ -6614,27 +6559,27 @@
         <v>72</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>210</v>
+        <v>105</v>
       </c>
       <c r="AG50" t="s" s="2">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="AH50" t="s" s="2">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="AI50" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AJ50" t="s" s="2">
-        <v>81</v>
+        <v>98</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -6642,7 +6587,7 @@
       </c>
       <c r="E51" s="2"/>
       <c r="F51" t="s" s="2">
-        <v>73</v>
+        <v>83</v>
       </c>
       <c r="G51" t="s" s="2">
         <v>83</v>
@@ -6657,13 +6602,13 @@
         <v>72</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>84</v>
+        <v>146</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>85</v>
+        <v>212</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>86</v>
+        <v>213</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" s="2"/>
@@ -6714,10 +6659,10 @@
         <v>72</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>87</v>
+        <v>211</v>
       </c>
       <c r="AG51" t="s" s="2">
-        <v>73</v>
+        <v>83</v>
       </c>
       <c r="AH51" t="s" s="2">
         <v>83</v>
@@ -6738,14 +6683,14 @@
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
-        <v>89</v>
+        <v>72</v>
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
         <v>73</v>
       </c>
       <c r="G52" t="s" s="2">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="H52" t="s" s="2">
         <v>72</v>
@@ -6757,17 +6702,15 @@
         <v>72</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>90</v>
+        <v>215</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>91</v>
+        <v>216</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="N52" t="s" s="2">
-        <v>93</v>
-      </c>
+        <v>217</v>
+      </c>
+      <c r="N52" s="2"/>
       <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
         <v>72</v>
@@ -6804,75 +6747,71 @@
         <v>72</v>
       </c>
       <c r="AB52" t="s" s="2">
-        <v>94</v>
+        <v>72</v>
       </c>
       <c r="AC52" t="s" s="2">
-        <v>95</v>
+        <v>72</v>
       </c>
       <c r="AD52" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AE52" t="s" s="2">
-        <v>96</v>
+        <v>72</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>97</v>
+        <v>214</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AH52" t="s" s="2">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="AI52" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>98</v>
+        <v>72</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
-        <v>100</v>
+        <v>72</v>
       </c>
       <c r="E53" s="2"/>
       <c r="F53" t="s" s="2">
         <v>73</v>
       </c>
       <c r="G53" t="s" s="2">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="H53" t="s" s="2">
         <v>72</v>
       </c>
       <c r="I53" t="s" s="2">
-        <v>101</v>
+        <v>72</v>
       </c>
       <c r="J53" t="s" s="2">
-        <v>101</v>
+        <v>72</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>90</v>
+        <v>123</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>102</v>
+        <v>219</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="N53" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="O53" t="s" s="2">
-        <v>104</v>
-      </c>
+        <v>220</v>
+      </c>
+      <c r="N53" s="2"/>
+      <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
         <v>72</v>
       </c>
@@ -6920,27 +6859,27 @@
         <v>72</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>105</v>
+        <v>218</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AH53" t="s" s="2">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="AI53" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AJ53" t="s" s="2">
-        <v>98</v>
+        <v>72</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -6963,13 +6902,13 @@
         <v>72</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>129</v>
+        <v>222</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>217</v>
+        <v>223</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>218</v>
+        <v>224</v>
       </c>
       <c r="N54" s="2"/>
       <c r="O54" s="2"/>
@@ -7020,7 +6959,7 @@
         <v>72</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>83</v>
@@ -7037,10 +6976,10 @@
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>219</v>
+        <v>225</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>219</v>
+        <v>225</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -7063,13 +7002,13 @@
         <v>72</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>129</v>
+        <v>113</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>220</v>
+        <v>226</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>221</v>
+        <v>227</v>
       </c>
       <c r="N55" s="2"/>
       <c r="O55" s="2"/>
@@ -7120,7 +7059,7 @@
         <v>72</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>219</v>
+        <v>225</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>73</v>
@@ -7137,10 +7076,10 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>222</v>
+        <v>228</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>222</v>
+        <v>228</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -7163,13 +7102,13 @@
         <v>72</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>84</v>
+        <v>123</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>223</v>
+        <v>229</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>224</v>
+        <v>230</v>
       </c>
       <c r="N56" s="2"/>
       <c r="O56" s="2"/>
@@ -7220,7 +7159,7 @@
         <v>72</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>222</v>
+        <v>228</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>73</v>
@@ -7237,10 +7176,10 @@
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>225</v>
+        <v>231</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>225</v>
+        <v>231</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -7263,13 +7202,13 @@
         <v>72</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>129</v>
+        <v>113</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>226</v>
+        <v>232</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>227</v>
+        <v>233</v>
       </c>
       <c r="N57" s="2"/>
       <c r="O57" s="2"/>
@@ -7320,7 +7259,7 @@
         <v>72</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>225</v>
+        <v>231</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>73</v>
@@ -7337,10 +7276,10 @@
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>228</v>
+        <v>234</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>228</v>
+        <v>234</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -7363,13 +7302,13 @@
         <v>72</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>229</v>
+        <v>235</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="N58" s="2"/>
       <c r="O58" s="2"/>
@@ -7420,7 +7359,7 @@
         <v>72</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>228</v>
+        <v>234</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>73</v>
@@ -7432,15 +7371,15 @@
         <v>72</v>
       </c>
       <c r="AJ58" t="s" s="2">
-        <v>72</v>
+        <v>81</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>231</v>
+        <v>237</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>231</v>
+        <v>237</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -7463,13 +7402,13 @@
         <v>72</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>232</v>
+        <v>85</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>233</v>
+        <v>86</v>
       </c>
       <c r="N59" s="2"/>
       <c r="O59" s="2"/>
@@ -7520,7 +7459,7 @@
         <v>72</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>231</v>
+        <v>87</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>73</v>
@@ -7532,26 +7471,26 @@
         <v>72</v>
       </c>
       <c r="AJ59" t="s" s="2">
-        <v>81</v>
+        <v>72</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
-        <v>72</v>
+        <v>89</v>
       </c>
       <c r="E60" s="2"/>
       <c r="F60" t="s" s="2">
         <v>73</v>
       </c>
       <c r="G60" t="s" s="2">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="H60" t="s" s="2">
         <v>72</v>
@@ -7563,15 +7502,17 @@
         <v>72</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>86</v>
-      </c>
-      <c r="N60" s="2"/>
+        <v>92</v>
+      </c>
+      <c r="N60" t="s" s="2">
+        <v>93</v>
+      </c>
       <c r="O60" s="2"/>
       <c r="P60" t="s" s="2">
         <v>72</v>
@@ -7608,43 +7549,43 @@
         <v>72</v>
       </c>
       <c r="AB60" t="s" s="2">
-        <v>72</v>
+        <v>94</v>
       </c>
       <c r="AC60" t="s" s="2">
-        <v>72</v>
+        <v>95</v>
       </c>
       <c r="AD60" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AE60" t="s" s="2">
-        <v>72</v>
+        <v>96</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>87</v>
+        <v>97</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AH60" t="s" s="2">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="AI60" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AJ60" t="s" s="2">
-        <v>72</v>
+        <v>98</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
-        <v>89</v>
+        <v>100</v>
       </c>
       <c r="E61" s="2"/>
       <c r="F61" t="s" s="2">
@@ -7657,24 +7598,26 @@
         <v>72</v>
       </c>
       <c r="I61" t="s" s="2">
-        <v>72</v>
+        <v>101</v>
       </c>
       <c r="J61" t="s" s="2">
-        <v>72</v>
+        <v>101</v>
       </c>
       <c r="K61" t="s" s="2">
         <v>90</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>91</v>
+        <v>102</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>92</v>
+        <v>103</v>
       </c>
       <c r="N61" t="s" s="2">
         <v>93</v>
       </c>
-      <c r="O61" s="2"/>
+      <c r="O61" t="s" s="2">
+        <v>104</v>
+      </c>
       <c r="P61" t="s" s="2">
         <v>72</v>
       </c>
@@ -7710,19 +7653,19 @@
         <v>72</v>
       </c>
       <c r="AB61" t="s" s="2">
-        <v>94</v>
+        <v>72</v>
       </c>
       <c r="AC61" t="s" s="2">
-        <v>95</v>
+        <v>72</v>
       </c>
       <c r="AD61" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AE61" t="s" s="2">
-        <v>96</v>
+        <v>72</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>97</v>
+        <v>105</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>73</v>
@@ -7739,46 +7682,42 @@
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
-        <v>100</v>
+        <v>72</v>
       </c>
       <c r="E62" s="2"/>
       <c r="F62" t="s" s="2">
         <v>73</v>
       </c>
       <c r="G62" t="s" s="2">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="H62" t="s" s="2">
         <v>72</v>
       </c>
       <c r="I62" t="s" s="2">
-        <v>101</v>
+        <v>72</v>
       </c>
       <c r="J62" t="s" s="2">
-        <v>101</v>
+        <v>72</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>90</v>
+        <v>146</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>102</v>
+        <v>241</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="N62" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="O62" t="s" s="2">
-        <v>104</v>
-      </c>
+        <v>242</v>
+      </c>
+      <c r="N62" s="2"/>
+      <c r="O62" s="2"/>
       <c r="P62" t="s" s="2">
         <v>72</v>
       </c>
@@ -7826,27 +7765,27 @@
         <v>72</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>105</v>
+        <v>240</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AH62" t="s" s="2">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="AI62" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AJ62" t="s" s="2">
-        <v>98</v>
+        <v>72</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>237</v>
+        <v>243</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>237</v>
+        <v>243</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -7869,13 +7808,13 @@
         <v>72</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>139</v>
+        <v>146</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>238</v>
+        <v>244</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>239</v>
+        <v>245</v>
       </c>
       <c r="N63" s="2"/>
       <c r="O63" s="2"/>
@@ -7926,7 +7865,7 @@
         <v>72</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>237</v>
+        <v>243</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>73</v>
@@ -7943,10 +7882,10 @@
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>240</v>
+        <v>246</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>240</v>
+        <v>246</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -7969,13 +7908,13 @@
         <v>72</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>139</v>
+        <v>146</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>241</v>
+        <v>247</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>242</v>
+        <v>248</v>
       </c>
       <c r="N64" s="2"/>
       <c r="O64" s="2"/>
@@ -8026,7 +7965,7 @@
         <v>72</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>240</v>
+        <v>246</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>73</v>
@@ -8043,10 +7982,10 @@
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>243</v>
+        <v>249</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>243</v>
+        <v>249</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -8069,13 +8008,13 @@
         <v>72</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>139</v>
+        <v>78</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>244</v>
+        <v>250</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>245</v>
+        <v>251</v>
       </c>
       <c r="N65" s="2"/>
       <c r="O65" s="2"/>
@@ -8126,7 +8065,7 @@
         <v>72</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>243</v>
+        <v>249</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>73</v>
@@ -8138,15 +8077,15 @@
         <v>72</v>
       </c>
       <c r="AJ65" t="s" s="2">
-        <v>72</v>
+        <v>81</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>246</v>
+        <v>252</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>246</v>
+        <v>252</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -8169,13 +8108,13 @@
         <v>72</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>247</v>
+        <v>85</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>248</v>
+        <v>86</v>
       </c>
       <c r="N66" s="2"/>
       <c r="O66" s="2"/>
@@ -8226,7 +8165,7 @@
         <v>72</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>246</v>
+        <v>87</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>73</v>
@@ -8238,26 +8177,26 @@
         <v>72</v>
       </c>
       <c r="AJ66" t="s" s="2">
-        <v>81</v>
+        <v>72</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
-        <v>72</v>
+        <v>89</v>
       </c>
       <c r="E67" s="2"/>
       <c r="F67" t="s" s="2">
         <v>73</v>
       </c>
       <c r="G67" t="s" s="2">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="H67" t="s" s="2">
         <v>72</v>
@@ -8269,15 +8208,17 @@
         <v>72</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>86</v>
-      </c>
-      <c r="N67" s="2"/>
+        <v>92</v>
+      </c>
+      <c r="N67" t="s" s="2">
+        <v>93</v>
+      </c>
       <c r="O67" s="2"/>
       <c r="P67" t="s" s="2">
         <v>72</v>
@@ -8314,43 +8255,43 @@
         <v>72</v>
       </c>
       <c r="AB67" t="s" s="2">
-        <v>72</v>
+        <v>94</v>
       </c>
       <c r="AC67" t="s" s="2">
-        <v>72</v>
+        <v>95</v>
       </c>
       <c r="AD67" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AE67" t="s" s="2">
-        <v>72</v>
+        <v>96</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>87</v>
+        <v>97</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AH67" t="s" s="2">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="AI67" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AJ67" t="s" s="2">
-        <v>72</v>
+        <v>98</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
-        <v>89</v>
+        <v>100</v>
       </c>
       <c r="E68" s="2"/>
       <c r="F68" t="s" s="2">
@@ -8363,24 +8304,26 @@
         <v>72</v>
       </c>
       <c r="I68" t="s" s="2">
-        <v>72</v>
+        <v>101</v>
       </c>
       <c r="J68" t="s" s="2">
-        <v>72</v>
+        <v>101</v>
       </c>
       <c r="K68" t="s" s="2">
         <v>90</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>91</v>
+        <v>102</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>92</v>
+        <v>103</v>
       </c>
       <c r="N68" t="s" s="2">
         <v>93</v>
       </c>
-      <c r="O68" s="2"/>
+      <c r="O68" t="s" s="2">
+        <v>104</v>
+      </c>
       <c r="P68" t="s" s="2">
         <v>72</v>
       </c>
@@ -8416,19 +8359,19 @@
         <v>72</v>
       </c>
       <c r="AB68" t="s" s="2">
-        <v>94</v>
+        <v>72</v>
       </c>
       <c r="AC68" t="s" s="2">
-        <v>95</v>
+        <v>72</v>
       </c>
       <c r="AD68" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AE68" t="s" s="2">
-        <v>96</v>
+        <v>72</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>97</v>
+        <v>105</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>73</v>
@@ -8445,46 +8388,42 @@
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
-        <v>100</v>
+        <v>72</v>
       </c>
       <c r="E69" s="2"/>
       <c r="F69" t="s" s="2">
         <v>73</v>
       </c>
       <c r="G69" t="s" s="2">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="H69" t="s" s="2">
         <v>72</v>
       </c>
       <c r="I69" t="s" s="2">
-        <v>101</v>
+        <v>72</v>
       </c>
       <c r="J69" t="s" s="2">
-        <v>101</v>
+        <v>72</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>90</v>
+        <v>146</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>102</v>
+        <v>256</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="N69" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="O69" t="s" s="2">
-        <v>104</v>
-      </c>
+        <v>257</v>
+      </c>
+      <c r="N69" s="2"/>
+      <c r="O69" s="2"/>
       <c r="P69" t="s" s="2">
         <v>72</v>
       </c>
@@ -8532,27 +8471,27 @@
         <v>72</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>105</v>
+        <v>255</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AH69" t="s" s="2">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="AI69" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AJ69" t="s" s="2">
-        <v>98</v>
+        <v>72</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
-        <v>252</v>
+        <v>258</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>252</v>
+        <v>258</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -8575,13 +8514,13 @@
         <v>72</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>139</v>
+        <v>113</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>253</v>
+        <v>259</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>254</v>
+        <v>260</v>
       </c>
       <c r="N70" s="2"/>
       <c r="O70" s="2"/>
@@ -8632,7 +8571,7 @@
         <v>72</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>252</v>
+        <v>258</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>73</v>
@@ -8649,10 +8588,10 @@
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>255</v>
+        <v>261</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>255</v>
+        <v>261</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -8675,13 +8614,13 @@
         <v>72</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>84</v>
+        <v>113</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>256</v>
+        <v>262</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>257</v>
+        <v>263</v>
       </c>
       <c r="N71" s="2"/>
       <c r="O71" s="2"/>
@@ -8732,7 +8671,7 @@
         <v>72</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>255</v>
+        <v>261</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>73</v>
@@ -8749,10 +8688,10 @@
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
-        <v>258</v>
+        <v>264</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>258</v>
+        <v>264</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -8763,7 +8702,7 @@
         <v>73</v>
       </c>
       <c r="G72" t="s" s="2">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="H72" t="s" s="2">
         <v>72</v>
@@ -8775,13 +8714,13 @@
         <v>72</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>84</v>
+        <v>146</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>260</v>
+        <v>266</v>
       </c>
       <c r="N72" s="2"/>
       <c r="O72" s="2"/>
@@ -8832,13 +8771,13 @@
         <v>72</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>258</v>
+        <v>264</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AH72" t="s" s="2">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="AI72" t="s" s="2">
         <v>72</v>
@@ -8849,10 +8788,10 @@
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
-        <v>261</v>
+        <v>267</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>261</v>
+        <v>267</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -8863,7 +8802,7 @@
         <v>73</v>
       </c>
       <c r="G73" t="s" s="2">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="H73" t="s" s="2">
         <v>72</v>
@@ -8875,13 +8814,13 @@
         <v>72</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>139</v>
+        <v>78</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>262</v>
+        <v>268</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>263</v>
+        <v>269</v>
       </c>
       <c r="N73" s="2"/>
       <c r="O73" s="2"/>
@@ -8932,27 +8871,27 @@
         <v>72</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>261</v>
+        <v>267</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AH73" t="s" s="2">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="AI73" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AJ73" t="s" s="2">
-        <v>72</v>
+        <v>81</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
-        <v>264</v>
+        <v>270</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>264</v>
+        <v>270</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -8975,13 +8914,13 @@
         <v>72</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>265</v>
+        <v>85</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>266</v>
+        <v>86</v>
       </c>
       <c r="N74" s="2"/>
       <c r="O74" s="2"/>
@@ -9032,7 +8971,7 @@
         <v>72</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>264</v>
+        <v>87</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>73</v>
@@ -9044,26 +8983,26 @@
         <v>72</v>
       </c>
       <c r="AJ74" t="s" s="2">
-        <v>81</v>
+        <v>72</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
-        <v>72</v>
+        <v>89</v>
       </c>
       <c r="E75" s="2"/>
       <c r="F75" t="s" s="2">
         <v>73</v>
       </c>
       <c r="G75" t="s" s="2">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="H75" t="s" s="2">
         <v>72</v>
@@ -9075,15 +9014,17 @@
         <v>72</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>86</v>
-      </c>
-      <c r="N75" s="2"/>
+        <v>92</v>
+      </c>
+      <c r="N75" t="s" s="2">
+        <v>93</v>
+      </c>
       <c r="O75" s="2"/>
       <c r="P75" t="s" s="2">
         <v>72</v>
@@ -9120,43 +9061,43 @@
         <v>72</v>
       </c>
       <c r="AB75" t="s" s="2">
-        <v>72</v>
+        <v>94</v>
       </c>
       <c r="AC75" t="s" s="2">
-        <v>72</v>
+        <v>95</v>
       </c>
       <c r="AD75" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AE75" t="s" s="2">
-        <v>72</v>
+        <v>96</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>87</v>
+        <v>97</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AH75" t="s" s="2">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="AI75" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AJ75" t="s" s="2">
-        <v>72</v>
+        <v>98</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="s" s="2">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
-        <v>89</v>
+        <v>100</v>
       </c>
       <c r="E76" s="2"/>
       <c r="F76" t="s" s="2">
@@ -9169,24 +9110,26 @@
         <v>72</v>
       </c>
       <c r="I76" t="s" s="2">
-        <v>72</v>
+        <v>101</v>
       </c>
       <c r="J76" t="s" s="2">
-        <v>72</v>
+        <v>101</v>
       </c>
       <c r="K76" t="s" s="2">
         <v>90</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>91</v>
+        <v>102</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>92</v>
+        <v>103</v>
       </c>
       <c r="N76" t="s" s="2">
         <v>93</v>
       </c>
-      <c r="O76" s="2"/>
+      <c r="O76" t="s" s="2">
+        <v>104</v>
+      </c>
       <c r="P76" t="s" s="2">
         <v>72</v>
       </c>
@@ -9222,19 +9165,19 @@
         <v>72</v>
       </c>
       <c r="AB76" t="s" s="2">
-        <v>94</v>
+        <v>72</v>
       </c>
       <c r="AC76" t="s" s="2">
-        <v>95</v>
+        <v>72</v>
       </c>
       <c r="AD76" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AE76" t="s" s="2">
-        <v>96</v>
+        <v>72</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>97</v>
+        <v>105</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>73</v>
@@ -9251,46 +9194,42 @@
     </row>
     <row r="77">
       <c r="A77" t="s" s="2">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
-        <v>100</v>
+        <v>72</v>
       </c>
       <c r="E77" s="2"/>
       <c r="F77" t="s" s="2">
         <v>73</v>
       </c>
       <c r="G77" t="s" s="2">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="H77" t="s" s="2">
         <v>72</v>
       </c>
       <c r="I77" t="s" s="2">
-        <v>101</v>
+        <v>72</v>
       </c>
       <c r="J77" t="s" s="2">
-        <v>101</v>
+        <v>72</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>90</v>
+        <v>113</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>102</v>
+        <v>274</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="N77" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="O77" t="s" s="2">
-        <v>104</v>
-      </c>
+        <v>275</v>
+      </c>
+      <c r="N77" s="2"/>
+      <c r="O77" s="2"/>
       <c r="P77" t="s" s="2">
         <v>72</v>
       </c>
@@ -9338,27 +9277,27 @@
         <v>72</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>105</v>
+        <v>273</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AH77" t="s" s="2">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="AI77" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AJ77" t="s" s="2">
-        <v>98</v>
+        <v>72</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="s" s="2">
-        <v>270</v>
+        <v>276</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>270</v>
+        <v>276</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -9381,13 +9320,13 @@
         <v>72</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>84</v>
+        <v>146</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>271</v>
+        <v>277</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>272</v>
+        <v>278</v>
       </c>
       <c r="N78" s="2"/>
       <c r="O78" s="2"/>
@@ -9438,7 +9377,7 @@
         <v>72</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>270</v>
+        <v>276</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>73</v>
@@ -9455,10 +9394,10 @@
     </row>
     <row r="79">
       <c r="A79" t="s" s="2">
-        <v>273</v>
+        <v>279</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>273</v>
+        <v>279</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -9481,13 +9420,13 @@
         <v>72</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>139</v>
+        <v>78</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>274</v>
+        <v>280</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>275</v>
+        <v>281</v>
       </c>
       <c r="N79" s="2"/>
       <c r="O79" s="2"/>
@@ -9538,7 +9477,7 @@
         <v>72</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>273</v>
+        <v>279</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>73</v>
@@ -9550,15 +9489,15 @@
         <v>72</v>
       </c>
       <c r="AJ79" t="s" s="2">
-        <v>72</v>
+        <v>81</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="s" s="2">
-        <v>276</v>
+        <v>282</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>276</v>
+        <v>282</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -9581,13 +9520,13 @@
         <v>72</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>277</v>
+        <v>85</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>278</v>
+        <v>86</v>
       </c>
       <c r="N80" s="2"/>
       <c r="O80" s="2"/>
@@ -9638,7 +9577,7 @@
         <v>72</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>276</v>
+        <v>87</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>73</v>
@@ -9650,26 +9589,26 @@
         <v>72</v>
       </c>
       <c r="AJ80" t="s" s="2">
-        <v>81</v>
+        <v>72</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="s" s="2">
-        <v>279</v>
+        <v>283</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>279</v>
+        <v>283</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
-        <v>72</v>
+        <v>89</v>
       </c>
       <c r="E81" s="2"/>
       <c r="F81" t="s" s="2">
         <v>73</v>
       </c>
       <c r="G81" t="s" s="2">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="H81" t="s" s="2">
         <v>72</v>
@@ -9681,15 +9620,17 @@
         <v>72</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>86</v>
-      </c>
-      <c r="N81" s="2"/>
+        <v>92</v>
+      </c>
+      <c r="N81" t="s" s="2">
+        <v>93</v>
+      </c>
       <c r="O81" s="2"/>
       <c r="P81" t="s" s="2">
         <v>72</v>
@@ -9726,43 +9667,43 @@
         <v>72</v>
       </c>
       <c r="AB81" t="s" s="2">
-        <v>72</v>
+        <v>94</v>
       </c>
       <c r="AC81" t="s" s="2">
-        <v>72</v>
+        <v>95</v>
       </c>
       <c r="AD81" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AE81" t="s" s="2">
-        <v>72</v>
+        <v>96</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>87</v>
+        <v>97</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AH81" t="s" s="2">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="AI81" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AJ81" t="s" s="2">
-        <v>72</v>
+        <v>98</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="s" s="2">
-        <v>280</v>
+        <v>284</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>280</v>
+        <v>284</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
-        <v>89</v>
+        <v>100</v>
       </c>
       <c r="E82" s="2"/>
       <c r="F82" t="s" s="2">
@@ -9775,24 +9716,26 @@
         <v>72</v>
       </c>
       <c r="I82" t="s" s="2">
-        <v>72</v>
+        <v>101</v>
       </c>
       <c r="J82" t="s" s="2">
-        <v>72</v>
+        <v>101</v>
       </c>
       <c r="K82" t="s" s="2">
         <v>90</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>91</v>
+        <v>102</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>92</v>
+        <v>103</v>
       </c>
       <c r="N82" t="s" s="2">
         <v>93</v>
       </c>
-      <c r="O82" s="2"/>
+      <c r="O82" t="s" s="2">
+        <v>104</v>
+      </c>
       <c r="P82" t="s" s="2">
         <v>72</v>
       </c>
@@ -9828,19 +9771,19 @@
         <v>72</v>
       </c>
       <c r="AB82" t="s" s="2">
-        <v>94</v>
+        <v>72</v>
       </c>
       <c r="AC82" t="s" s="2">
-        <v>95</v>
+        <v>72</v>
       </c>
       <c r="AD82" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AE82" t="s" s="2">
-        <v>96</v>
+        <v>72</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>97</v>
+        <v>105</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>73</v>
@@ -9857,46 +9800,42 @@
     </row>
     <row r="83">
       <c r="A83" t="s" s="2">
-        <v>281</v>
+        <v>285</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>281</v>
+        <v>285</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
-        <v>100</v>
+        <v>72</v>
       </c>
       <c r="E83" s="2"/>
       <c r="F83" t="s" s="2">
-        <v>73</v>
+        <v>83</v>
       </c>
       <c r="G83" t="s" s="2">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="H83" t="s" s="2">
         <v>72</v>
       </c>
       <c r="I83" t="s" s="2">
-        <v>101</v>
+        <v>72</v>
       </c>
       <c r="J83" t="s" s="2">
-        <v>101</v>
+        <v>72</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>90</v>
+        <v>146</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>102</v>
+        <v>286</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="N83" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="O83" t="s" s="2">
-        <v>104</v>
-      </c>
+        <v>287</v>
+      </c>
+      <c r="N83" s="2"/>
+      <c r="O83" s="2"/>
       <c r="P83" t="s" s="2">
         <v>72</v>
       </c>
@@ -9944,27 +9883,27 @@
         <v>72</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>105</v>
+        <v>285</v>
       </c>
       <c r="AG83" t="s" s="2">
-        <v>73</v>
+        <v>83</v>
       </c>
       <c r="AH83" t="s" s="2">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="AI83" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AJ83" t="s" s="2">
-        <v>98</v>
+        <v>72</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="s" s="2">
-        <v>282</v>
+        <v>288</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>282</v>
+        <v>288</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -9972,7 +9911,7 @@
       </c>
       <c r="E84" s="2"/>
       <c r="F84" t="s" s="2">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="G84" t="s" s="2">
         <v>83</v>
@@ -9987,13 +9926,13 @@
         <v>72</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>139</v>
+        <v>78</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>283</v>
+        <v>289</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>284</v>
+        <v>290</v>
       </c>
       <c r="N84" s="2"/>
       <c r="O84" s="2"/>
@@ -10044,10 +9983,10 @@
         <v>72</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>282</v>
+        <v>288</v>
       </c>
       <c r="AG84" t="s" s="2">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="AH84" t="s" s="2">
         <v>83</v>
@@ -10056,15 +9995,15 @@
         <v>72</v>
       </c>
       <c r="AJ84" t="s" s="2">
-        <v>72</v>
+        <v>81</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="s" s="2">
-        <v>285</v>
+        <v>291</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>285</v>
+        <v>291</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -10087,13 +10026,13 @@
         <v>72</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>286</v>
+        <v>85</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>287</v>
+        <v>86</v>
       </c>
       <c r="N85" s="2"/>
       <c r="O85" s="2"/>
@@ -10144,7 +10083,7 @@
         <v>72</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>285</v>
+        <v>87</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>73</v>
@@ -10156,26 +10095,26 @@
         <v>72</v>
       </c>
       <c r="AJ85" t="s" s="2">
-        <v>81</v>
+        <v>72</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="s" s="2">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
-        <v>72</v>
+        <v>89</v>
       </c>
       <c r="E86" s="2"/>
       <c r="F86" t="s" s="2">
         <v>73</v>
       </c>
       <c r="G86" t="s" s="2">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="H86" t="s" s="2">
         <v>72</v>
@@ -10187,15 +10126,17 @@
         <v>72</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>86</v>
-      </c>
-      <c r="N86" s="2"/>
+        <v>92</v>
+      </c>
+      <c r="N86" t="s" s="2">
+        <v>93</v>
+      </c>
       <c r="O86" s="2"/>
       <c r="P86" t="s" s="2">
         <v>72</v>
@@ -10232,43 +10173,43 @@
         <v>72</v>
       </c>
       <c r="AB86" t="s" s="2">
-        <v>72</v>
+        <v>94</v>
       </c>
       <c r="AC86" t="s" s="2">
-        <v>72</v>
+        <v>95</v>
       </c>
       <c r="AD86" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AE86" t="s" s="2">
-        <v>72</v>
+        <v>96</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>87</v>
+        <v>97</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AH86" t="s" s="2">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="AI86" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AJ86" t="s" s="2">
-        <v>72</v>
+        <v>98</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="s" s="2">
-        <v>289</v>
+        <v>293</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>289</v>
+        <v>293</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
-        <v>89</v>
+        <v>100</v>
       </c>
       <c r="E87" s="2"/>
       <c r="F87" t="s" s="2">
@@ -10281,24 +10222,26 @@
         <v>72</v>
       </c>
       <c r="I87" t="s" s="2">
-        <v>72</v>
+        <v>101</v>
       </c>
       <c r="J87" t="s" s="2">
-        <v>72</v>
+        <v>101</v>
       </c>
       <c r="K87" t="s" s="2">
         <v>90</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>91</v>
+        <v>102</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>92</v>
+        <v>103</v>
       </c>
       <c r="N87" t="s" s="2">
         <v>93</v>
       </c>
-      <c r="O87" s="2"/>
+      <c r="O87" t="s" s="2">
+        <v>104</v>
+      </c>
       <c r="P87" t="s" s="2">
         <v>72</v>
       </c>
@@ -10334,19 +10277,19 @@
         <v>72</v>
       </c>
       <c r="AB87" t="s" s="2">
-        <v>94</v>
+        <v>72</v>
       </c>
       <c r="AC87" t="s" s="2">
-        <v>95</v>
+        <v>72</v>
       </c>
       <c r="AD87" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AE87" t="s" s="2">
-        <v>96</v>
+        <v>72</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>97</v>
+        <v>105</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>73</v>
@@ -10363,46 +10306,42 @@
     </row>
     <row r="88">
       <c r="A88" t="s" s="2">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
-        <v>100</v>
+        <v>72</v>
       </c>
       <c r="E88" s="2"/>
       <c r="F88" t="s" s="2">
-        <v>73</v>
+        <v>83</v>
       </c>
       <c r="G88" t="s" s="2">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="H88" t="s" s="2">
         <v>72</v>
       </c>
       <c r="I88" t="s" s="2">
-        <v>101</v>
+        <v>72</v>
       </c>
       <c r="J88" t="s" s="2">
-        <v>101</v>
+        <v>72</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>90</v>
+        <v>113</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>102</v>
+        <v>295</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="N88" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="O88" t="s" s="2">
-        <v>104</v>
-      </c>
+        <v>296</v>
+      </c>
+      <c r="N88" s="2"/>
+      <c r="O88" s="2"/>
       <c r="P88" t="s" s="2">
         <v>72</v>
       </c>
@@ -10450,27 +10389,27 @@
         <v>72</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>105</v>
+        <v>294</v>
       </c>
       <c r="AG88" t="s" s="2">
-        <v>73</v>
+        <v>83</v>
       </c>
       <c r="AH88" t="s" s="2">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="AI88" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AJ88" t="s" s="2">
-        <v>98</v>
+        <v>72</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="s" s="2">
-        <v>291</v>
+        <v>297</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>291</v>
+        <v>297</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -10478,7 +10417,7 @@
       </c>
       <c r="E89" s="2"/>
       <c r="F89" t="s" s="2">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="G89" t="s" s="2">
         <v>83</v>
@@ -10493,13 +10432,13 @@
         <v>72</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>84</v>
+        <v>146</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>292</v>
+        <v>298</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>293</v>
+        <v>299</v>
       </c>
       <c r="N89" s="2"/>
       <c r="O89" s="2"/>
@@ -10550,10 +10489,10 @@
         <v>72</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>291</v>
+        <v>297</v>
       </c>
       <c r="AG89" t="s" s="2">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="AH89" t="s" s="2">
         <v>83</v>
@@ -10567,10 +10506,10 @@
     </row>
     <row r="90">
       <c r="A90" t="s" s="2">
-        <v>294</v>
+        <v>300</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>294</v>
+        <v>300</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -10581,7 +10520,7 @@
         <v>73</v>
       </c>
       <c r="G90" t="s" s="2">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="H90" t="s" s="2">
         <v>72</v>
@@ -10593,13 +10532,13 @@
         <v>72</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>139</v>
+        <v>146</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>295</v>
+        <v>301</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>296</v>
+        <v>302</v>
       </c>
       <c r="N90" s="2"/>
       <c r="O90" s="2"/>
@@ -10650,13 +10589,13 @@
         <v>72</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>294</v>
+        <v>300</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AH90" t="s" s="2">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="AI90" t="s" s="2">
         <v>72</v>
@@ -10667,10 +10606,10 @@
     </row>
     <row r="91">
       <c r="A91" t="s" s="2">
-        <v>297</v>
+        <v>303</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>297</v>
+        <v>303</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -10681,7 +10620,7 @@
         <v>73</v>
       </c>
       <c r="G91" t="s" s="2">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="H91" t="s" s="2">
         <v>72</v>
@@ -10693,13 +10632,13 @@
         <v>72</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>139</v>
+        <v>78</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>298</v>
+        <v>304</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>299</v>
+        <v>305</v>
       </c>
       <c r="N91" s="2"/>
       <c r="O91" s="2"/>
@@ -10750,27 +10689,27 @@
         <v>72</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>297</v>
+        <v>303</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AH91" t="s" s="2">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="AI91" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AJ91" t="s" s="2">
-        <v>72</v>
+        <v>81</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="s" s="2">
-        <v>300</v>
+        <v>306</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>300</v>
+        <v>306</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -10793,13 +10732,13 @@
         <v>72</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>301</v>
+        <v>85</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>302</v>
+        <v>86</v>
       </c>
       <c r="N92" s="2"/>
       <c r="O92" s="2"/>
@@ -10850,7 +10789,7 @@
         <v>72</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>300</v>
+        <v>87</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>73</v>
@@ -10862,26 +10801,26 @@
         <v>72</v>
       </c>
       <c r="AJ92" t="s" s="2">
-        <v>81</v>
+        <v>72</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="s" s="2">
-        <v>303</v>
+        <v>307</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>303</v>
+        <v>307</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
-        <v>72</v>
+        <v>89</v>
       </c>
       <c r="E93" s="2"/>
       <c r="F93" t="s" s="2">
         <v>73</v>
       </c>
       <c r="G93" t="s" s="2">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="H93" t="s" s="2">
         <v>72</v>
@@ -10893,15 +10832,17 @@
         <v>72</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>86</v>
-      </c>
-      <c r="N93" s="2"/>
+        <v>92</v>
+      </c>
+      <c r="N93" t="s" s="2">
+        <v>93</v>
+      </c>
       <c r="O93" s="2"/>
       <c r="P93" t="s" s="2">
         <v>72</v>
@@ -10938,43 +10879,43 @@
         <v>72</v>
       </c>
       <c r="AB93" t="s" s="2">
-        <v>72</v>
+        <v>94</v>
       </c>
       <c r="AC93" t="s" s="2">
-        <v>72</v>
+        <v>95</v>
       </c>
       <c r="AD93" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AE93" t="s" s="2">
-        <v>72</v>
+        <v>96</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>87</v>
+        <v>97</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AH93" t="s" s="2">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="AI93" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AJ93" t="s" s="2">
-        <v>72</v>
+        <v>98</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="s" s="2">
-        <v>304</v>
+        <v>308</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>304</v>
+        <v>308</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
-        <v>89</v>
+        <v>100</v>
       </c>
       <c r="E94" s="2"/>
       <c r="F94" t="s" s="2">
@@ -10987,24 +10928,26 @@
         <v>72</v>
       </c>
       <c r="I94" t="s" s="2">
-        <v>72</v>
+        <v>101</v>
       </c>
       <c r="J94" t="s" s="2">
-        <v>72</v>
+        <v>101</v>
       </c>
       <c r="K94" t="s" s="2">
         <v>90</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>91</v>
+        <v>102</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>92</v>
+        <v>103</v>
       </c>
       <c r="N94" t="s" s="2">
         <v>93</v>
       </c>
-      <c r="O94" s="2"/>
+      <c r="O94" t="s" s="2">
+        <v>104</v>
+      </c>
       <c r="P94" t="s" s="2">
         <v>72</v>
       </c>
@@ -11040,19 +10983,19 @@
         <v>72</v>
       </c>
       <c r="AB94" t="s" s="2">
-        <v>94</v>
+        <v>72</v>
       </c>
       <c r="AC94" t="s" s="2">
-        <v>95</v>
+        <v>72</v>
       </c>
       <c r="AD94" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AE94" t="s" s="2">
-        <v>96</v>
+        <v>72</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>97</v>
+        <v>105</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>73</v>
@@ -11069,46 +11012,42 @@
     </row>
     <row r="95">
       <c r="A95" t="s" s="2">
-        <v>305</v>
+        <v>309</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>305</v>
+        <v>309</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
-        <v>100</v>
+        <v>72</v>
       </c>
       <c r="E95" s="2"/>
       <c r="F95" t="s" s="2">
-        <v>73</v>
+        <v>83</v>
       </c>
       <c r="G95" t="s" s="2">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="H95" t="s" s="2">
         <v>72</v>
       </c>
       <c r="I95" t="s" s="2">
-        <v>101</v>
+        <v>72</v>
       </c>
       <c r="J95" t="s" s="2">
-        <v>101</v>
+        <v>72</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>90</v>
+        <v>146</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>102</v>
+        <v>310</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="N95" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="O95" t="s" s="2">
-        <v>104</v>
-      </c>
+        <v>311</v>
+      </c>
+      <c r="N95" s="2"/>
+      <c r="O95" s="2"/>
       <c r="P95" t="s" s="2">
         <v>72</v>
       </c>
@@ -11156,27 +11095,27 @@
         <v>72</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>105</v>
+        <v>309</v>
       </c>
       <c r="AG95" t="s" s="2">
-        <v>73</v>
+        <v>83</v>
       </c>
       <c r="AH95" t="s" s="2">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="AI95" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AJ95" t="s" s="2">
-        <v>98</v>
+        <v>72</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="s" s="2">
-        <v>306</v>
+        <v>312</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>306</v>
+        <v>312</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -11184,7 +11123,7 @@
       </c>
       <c r="E96" s="2"/>
       <c r="F96" t="s" s="2">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="G96" t="s" s="2">
         <v>83</v>
@@ -11199,13 +11138,13 @@
         <v>72</v>
       </c>
       <c r="K96" t="s" s="2">
-        <v>139</v>
+        <v>146</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>307</v>
+        <v>313</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>308</v>
+        <v>314</v>
       </c>
       <c r="N96" s="2"/>
       <c r="O96" s="2"/>
@@ -11256,10 +11195,10 @@
         <v>72</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>306</v>
+        <v>312</v>
       </c>
       <c r="AG96" t="s" s="2">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="AH96" t="s" s="2">
         <v>83</v>
@@ -11273,10 +11212,10 @@
     </row>
     <row r="97">
       <c r="A97" t="s" s="2">
-        <v>309</v>
+        <v>315</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>309</v>
+        <v>315</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -11299,13 +11238,13 @@
         <v>72</v>
       </c>
       <c r="K97" t="s" s="2">
-        <v>139</v>
+        <v>78</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>310</v>
+        <v>316</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>311</v>
+        <v>317</v>
       </c>
       <c r="N97" s="2"/>
       <c r="O97" s="2"/>
@@ -11356,7 +11295,7 @@
         <v>72</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>309</v>
+        <v>315</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>73</v>
@@ -11368,15 +11307,15 @@
         <v>72</v>
       </c>
       <c r="AJ97" t="s" s="2">
-        <v>72</v>
+        <v>81</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="s" s="2">
-        <v>312</v>
+        <v>318</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>312</v>
+        <v>318</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -11399,13 +11338,13 @@
         <v>72</v>
       </c>
       <c r="K98" t="s" s="2">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>313</v>
+        <v>85</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>314</v>
+        <v>86</v>
       </c>
       <c r="N98" s="2"/>
       <c r="O98" s="2"/>
@@ -11456,7 +11395,7 @@
         <v>72</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>312</v>
+        <v>87</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>73</v>
@@ -11468,26 +11407,26 @@
         <v>72</v>
       </c>
       <c r="AJ98" t="s" s="2">
-        <v>81</v>
+        <v>72</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="s" s="2">
-        <v>315</v>
+        <v>319</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>315</v>
+        <v>319</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
-        <v>72</v>
+        <v>89</v>
       </c>
       <c r="E99" s="2"/>
       <c r="F99" t="s" s="2">
         <v>73</v>
       </c>
       <c r="G99" t="s" s="2">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="H99" t="s" s="2">
         <v>72</v>
@@ -11499,15 +11438,17 @@
         <v>72</v>
       </c>
       <c r="K99" t="s" s="2">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>86</v>
-      </c>
-      <c r="N99" s="2"/>
+        <v>92</v>
+      </c>
+      <c r="N99" t="s" s="2">
+        <v>93</v>
+      </c>
       <c r="O99" s="2"/>
       <c r="P99" t="s" s="2">
         <v>72</v>
@@ -11544,43 +11485,43 @@
         <v>72</v>
       </c>
       <c r="AB99" t="s" s="2">
-        <v>72</v>
+        <v>94</v>
       </c>
       <c r="AC99" t="s" s="2">
-        <v>72</v>
+        <v>95</v>
       </c>
       <c r="AD99" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AE99" t="s" s="2">
-        <v>72</v>
+        <v>96</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>87</v>
+        <v>97</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AH99" t="s" s="2">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="AI99" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AJ99" t="s" s="2">
-        <v>72</v>
+        <v>98</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="s" s="2">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
-        <v>89</v>
+        <v>100</v>
       </c>
       <c r="E100" s="2"/>
       <c r="F100" t="s" s="2">
@@ -11593,24 +11534,26 @@
         <v>72</v>
       </c>
       <c r="I100" t="s" s="2">
-        <v>72</v>
+        <v>101</v>
       </c>
       <c r="J100" t="s" s="2">
-        <v>72</v>
+        <v>101</v>
       </c>
       <c r="K100" t="s" s="2">
         <v>90</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>91</v>
+        <v>102</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>92</v>
+        <v>103</v>
       </c>
       <c r="N100" t="s" s="2">
         <v>93</v>
       </c>
-      <c r="O100" s="2"/>
+      <c r="O100" t="s" s="2">
+        <v>104</v>
+      </c>
       <c r="P100" t="s" s="2">
         <v>72</v>
       </c>
@@ -11646,19 +11589,19 @@
         <v>72</v>
       </c>
       <c r="AB100" t="s" s="2">
-        <v>94</v>
+        <v>72</v>
       </c>
       <c r="AC100" t="s" s="2">
-        <v>95</v>
+        <v>72</v>
       </c>
       <c r="AD100" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AE100" t="s" s="2">
-        <v>96</v>
+        <v>72</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>97</v>
+        <v>105</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>73</v>
@@ -11675,46 +11618,42 @@
     </row>
     <row r="101">
       <c r="A101" t="s" s="2">
-        <v>317</v>
+        <v>321</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>317</v>
+        <v>321</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
-        <v>100</v>
+        <v>72</v>
       </c>
       <c r="E101" s="2"/>
       <c r="F101" t="s" s="2">
-        <v>73</v>
+        <v>83</v>
       </c>
       <c r="G101" t="s" s="2">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="H101" t="s" s="2">
         <v>72</v>
       </c>
       <c r="I101" t="s" s="2">
-        <v>101</v>
+        <v>72</v>
       </c>
       <c r="J101" t="s" s="2">
-        <v>101</v>
+        <v>72</v>
       </c>
       <c r="K101" t="s" s="2">
-        <v>90</v>
+        <v>113</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>102</v>
+        <v>322</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="N101" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="O101" t="s" s="2">
-        <v>104</v>
-      </c>
+        <v>323</v>
+      </c>
+      <c r="N101" s="2"/>
+      <c r="O101" s="2"/>
       <c r="P101" t="s" s="2">
         <v>72</v>
       </c>
@@ -11762,27 +11701,27 @@
         <v>72</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>105</v>
+        <v>321</v>
       </c>
       <c r="AG101" t="s" s="2">
-        <v>73</v>
+        <v>83</v>
       </c>
       <c r="AH101" t="s" s="2">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="AI101" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AJ101" t="s" s="2">
-        <v>98</v>
+        <v>72</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="s" s="2">
-        <v>318</v>
+        <v>324</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>318</v>
+        <v>324</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -11790,7 +11729,7 @@
       </c>
       <c r="E102" s="2"/>
       <c r="F102" t="s" s="2">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="G102" t="s" s="2">
         <v>83</v>
@@ -11805,13 +11744,13 @@
         <v>72</v>
       </c>
       <c r="K102" t="s" s="2">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>319</v>
+        <v>325</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>320</v>
+        <v>326</v>
       </c>
       <c r="N102" s="2"/>
       <c r="O102" s="2"/>
@@ -11862,10 +11801,10 @@
         <v>72</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>318</v>
+        <v>324</v>
       </c>
       <c r="AG102" t="s" s="2">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="AH102" t="s" s="2">
         <v>83</v>
@@ -11874,15 +11813,15 @@
         <v>72</v>
       </c>
       <c r="AJ102" t="s" s="2">
-        <v>72</v>
+        <v>81</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="s" s="2">
-        <v>321</v>
+        <v>327</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>321</v>
+        <v>327</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -11905,13 +11844,13 @@
         <v>72</v>
       </c>
       <c r="K103" t="s" s="2">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>322</v>
+        <v>85</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>323</v>
+        <v>86</v>
       </c>
       <c r="N103" s="2"/>
       <c r="O103" s="2"/>
@@ -11962,7 +11901,7 @@
         <v>72</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>321</v>
+        <v>87</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>73</v>
@@ -11974,26 +11913,26 @@
         <v>72</v>
       </c>
       <c r="AJ103" t="s" s="2">
-        <v>81</v>
+        <v>72</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="s" s="2">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
-        <v>72</v>
+        <v>89</v>
       </c>
       <c r="E104" s="2"/>
       <c r="F104" t="s" s="2">
         <v>73</v>
       </c>
       <c r="G104" t="s" s="2">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="H104" t="s" s="2">
         <v>72</v>
@@ -12005,15 +11944,17 @@
         <v>72</v>
       </c>
       <c r="K104" t="s" s="2">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="L104" t="s" s="2">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="M104" t="s" s="2">
-        <v>86</v>
-      </c>
-      <c r="N104" s="2"/>
+        <v>92</v>
+      </c>
+      <c r="N104" t="s" s="2">
+        <v>93</v>
+      </c>
       <c r="O104" s="2"/>
       <c r="P104" t="s" s="2">
         <v>72</v>
@@ -12050,43 +11991,43 @@
         <v>72</v>
       </c>
       <c r="AB104" t="s" s="2">
-        <v>72</v>
+        <v>94</v>
       </c>
       <c r="AC104" t="s" s="2">
-        <v>72</v>
+        <v>95</v>
       </c>
       <c r="AD104" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AE104" t="s" s="2">
-        <v>72</v>
+        <v>96</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>87</v>
+        <v>97</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AH104" t="s" s="2">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="AI104" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AJ104" t="s" s="2">
-        <v>72</v>
+        <v>98</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="s" s="2">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
-        <v>89</v>
+        <v>100</v>
       </c>
       <c r="E105" s="2"/>
       <c r="F105" t="s" s="2">
@@ -12099,24 +12040,26 @@
         <v>72</v>
       </c>
       <c r="I105" t="s" s="2">
-        <v>72</v>
+        <v>101</v>
       </c>
       <c r="J105" t="s" s="2">
-        <v>72</v>
+        <v>101</v>
       </c>
       <c r="K105" t="s" s="2">
         <v>90</v>
       </c>
       <c r="L105" t="s" s="2">
-        <v>91</v>
+        <v>102</v>
       </c>
       <c r="M105" t="s" s="2">
-        <v>92</v>
+        <v>103</v>
       </c>
       <c r="N105" t="s" s="2">
         <v>93</v>
       </c>
-      <c r="O105" s="2"/>
+      <c r="O105" t="s" s="2">
+        <v>104</v>
+      </c>
       <c r="P105" t="s" s="2">
         <v>72</v>
       </c>
@@ -12152,19 +12095,19 @@
         <v>72</v>
       </c>
       <c r="AB105" t="s" s="2">
-        <v>94</v>
+        <v>72</v>
       </c>
       <c r="AC105" t="s" s="2">
-        <v>95</v>
+        <v>72</v>
       </c>
       <c r="AD105" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AE105" t="s" s="2">
-        <v>96</v>
+        <v>72</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>97</v>
+        <v>105</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>73</v>
@@ -12181,46 +12124,42 @@
     </row>
     <row r="106">
       <c r="A106" t="s" s="2">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
-        <v>100</v>
+        <v>72</v>
       </c>
       <c r="E106" s="2"/>
       <c r="F106" t="s" s="2">
-        <v>73</v>
+        <v>83</v>
       </c>
       <c r="G106" t="s" s="2">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="H106" t="s" s="2">
         <v>72</v>
       </c>
       <c r="I106" t="s" s="2">
-        <v>101</v>
+        <v>72</v>
       </c>
       <c r="J106" t="s" s="2">
-        <v>101</v>
+        <v>72</v>
       </c>
       <c r="K106" t="s" s="2">
-        <v>90</v>
+        <v>113</v>
       </c>
       <c r="L106" t="s" s="2">
-        <v>102</v>
+        <v>331</v>
       </c>
       <c r="M106" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="N106" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="O106" t="s" s="2">
-        <v>104</v>
-      </c>
+        <v>332</v>
+      </c>
+      <c r="N106" s="2"/>
+      <c r="O106" s="2"/>
       <c r="P106" t="s" s="2">
         <v>72</v>
       </c>
@@ -12268,27 +12207,27 @@
         <v>72</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>105</v>
+        <v>330</v>
       </c>
       <c r="AG106" t="s" s="2">
-        <v>73</v>
+        <v>83</v>
       </c>
       <c r="AH106" t="s" s="2">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="AI106" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AJ106" t="s" s="2">
-        <v>98</v>
+        <v>72</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="s" s="2">
-        <v>327</v>
+        <v>333</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>327</v>
+        <v>333</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -12311,13 +12250,13 @@
         <v>72</v>
       </c>
       <c r="K107" t="s" s="2">
-        <v>84</v>
+        <v>113</v>
       </c>
       <c r="L107" t="s" s="2">
-        <v>328</v>
+        <v>334</v>
       </c>
       <c r="M107" t="s" s="2">
-        <v>329</v>
+        <v>335</v>
       </c>
       <c r="N107" s="2"/>
       <c r="O107" s="2"/>
@@ -12368,7 +12307,7 @@
         <v>72</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>327</v>
+        <v>333</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>83</v>
@@ -12385,10 +12324,10 @@
     </row>
     <row r="108">
       <c r="A108" t="s" s="2">
-        <v>330</v>
+        <v>336</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>330</v>
+        <v>336</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -12396,10 +12335,10 @@
       </c>
       <c r="E108" s="2"/>
       <c r="F108" t="s" s="2">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="G108" t="s" s="2">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="H108" t="s" s="2">
         <v>72</v>
@@ -12411,13 +12350,13 @@
         <v>72</v>
       </c>
       <c r="K108" t="s" s="2">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="L108" t="s" s="2">
-        <v>331</v>
+        <v>337</v>
       </c>
       <c r="M108" t="s" s="2">
-        <v>332</v>
+        <v>338</v>
       </c>
       <c r="N108" s="2"/>
       <c r="O108" s="2"/>
@@ -12468,27 +12407,27 @@
         <v>72</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>330</v>
+        <v>336</v>
       </c>
       <c r="AG108" t="s" s="2">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="AH108" t="s" s="2">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="AI108" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AJ108" t="s" s="2">
-        <v>72</v>
+        <v>81</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="s" s="2">
-        <v>333</v>
+        <v>339</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>333</v>
+        <v>339</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -12499,7 +12438,7 @@
         <v>73</v>
       </c>
       <c r="G109" t="s" s="2">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="H109" t="s" s="2">
         <v>72</v>
@@ -12511,13 +12450,13 @@
         <v>72</v>
       </c>
       <c r="K109" t="s" s="2">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="L109" t="s" s="2">
-        <v>334</v>
+        <v>85</v>
       </c>
       <c r="M109" t="s" s="2">
-        <v>335</v>
+        <v>86</v>
       </c>
       <c r="N109" s="2"/>
       <c r="O109" s="2"/>
@@ -12568,38 +12507,38 @@
         <v>72</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>333</v>
+        <v>87</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AH109" t="s" s="2">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="AI109" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AJ109" t="s" s="2">
-        <v>81</v>
+        <v>72</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="s" s="2">
-        <v>336</v>
+        <v>340</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>336</v>
+        <v>340</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
-        <v>72</v>
+        <v>89</v>
       </c>
       <c r="E110" s="2"/>
       <c r="F110" t="s" s="2">
         <v>73</v>
       </c>
       <c r="G110" t="s" s="2">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="H110" t="s" s="2">
         <v>72</v>
@@ -12611,15 +12550,17 @@
         <v>72</v>
       </c>
       <c r="K110" t="s" s="2">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="L110" t="s" s="2">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="M110" t="s" s="2">
-        <v>86</v>
-      </c>
-      <c r="N110" s="2"/>
+        <v>92</v>
+      </c>
+      <c r="N110" t="s" s="2">
+        <v>93</v>
+      </c>
       <c r="O110" s="2"/>
       <c r="P110" t="s" s="2">
         <v>72</v>
@@ -12656,43 +12597,43 @@
         <v>72</v>
       </c>
       <c r="AB110" t="s" s="2">
-        <v>72</v>
+        <v>94</v>
       </c>
       <c r="AC110" t="s" s="2">
-        <v>72</v>
+        <v>95</v>
       </c>
       <c r="AD110" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AE110" t="s" s="2">
-        <v>72</v>
+        <v>96</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>87</v>
+        <v>97</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AH110" t="s" s="2">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="AI110" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AJ110" t="s" s="2">
-        <v>72</v>
+        <v>98</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="s" s="2">
-        <v>337</v>
+        <v>341</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>337</v>
+        <v>341</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
-        <v>89</v>
+        <v>100</v>
       </c>
       <c r="E111" s="2"/>
       <c r="F111" t="s" s="2">
@@ -12705,24 +12646,26 @@
         <v>72</v>
       </c>
       <c r="I111" t="s" s="2">
-        <v>72</v>
+        <v>101</v>
       </c>
       <c r="J111" t="s" s="2">
-        <v>72</v>
+        <v>101</v>
       </c>
       <c r="K111" t="s" s="2">
         <v>90</v>
       </c>
       <c r="L111" t="s" s="2">
-        <v>91</v>
+        <v>102</v>
       </c>
       <c r="M111" t="s" s="2">
-        <v>92</v>
+        <v>103</v>
       </c>
       <c r="N111" t="s" s="2">
         <v>93</v>
       </c>
-      <c r="O111" s="2"/>
+      <c r="O111" t="s" s="2">
+        <v>104</v>
+      </c>
       <c r="P111" t="s" s="2">
         <v>72</v>
       </c>
@@ -12758,19 +12701,19 @@
         <v>72</v>
       </c>
       <c r="AB111" t="s" s="2">
-        <v>94</v>
+        <v>72</v>
       </c>
       <c r="AC111" t="s" s="2">
-        <v>95</v>
+        <v>72</v>
       </c>
       <c r="AD111" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AE111" t="s" s="2">
-        <v>96</v>
+        <v>72</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>97</v>
+        <v>105</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>73</v>
@@ -12787,46 +12730,42 @@
     </row>
     <row r="112">
       <c r="A112" t="s" s="2">
-        <v>338</v>
+        <v>342</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>338</v>
+        <v>342</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
-        <v>100</v>
+        <v>72</v>
       </c>
       <c r="E112" s="2"/>
       <c r="F112" t="s" s="2">
-        <v>73</v>
+        <v>83</v>
       </c>
       <c r="G112" t="s" s="2">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="H112" t="s" s="2">
         <v>72</v>
       </c>
       <c r="I112" t="s" s="2">
-        <v>101</v>
+        <v>72</v>
       </c>
       <c r="J112" t="s" s="2">
-        <v>101</v>
+        <v>72</v>
       </c>
       <c r="K112" t="s" s="2">
-        <v>90</v>
+        <v>146</v>
       </c>
       <c r="L112" t="s" s="2">
-        <v>102</v>
+        <v>343</v>
       </c>
       <c r="M112" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="N112" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="O112" t="s" s="2">
-        <v>104</v>
-      </c>
+        <v>344</v>
+      </c>
+      <c r="N112" s="2"/>
+      <c r="O112" s="2"/>
       <c r="P112" t="s" s="2">
         <v>72</v>
       </c>
@@ -12874,27 +12813,27 @@
         <v>72</v>
       </c>
       <c r="AF112" t="s" s="2">
-        <v>105</v>
+        <v>342</v>
       </c>
       <c r="AG112" t="s" s="2">
-        <v>73</v>
+        <v>83</v>
       </c>
       <c r="AH112" t="s" s="2">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="AI112" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AJ112" t="s" s="2">
-        <v>98</v>
+        <v>72</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="s" s="2">
-        <v>339</v>
+        <v>345</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>339</v>
+        <v>345</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -12902,7 +12841,7 @@
       </c>
       <c r="E113" s="2"/>
       <c r="F113" t="s" s="2">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="G113" t="s" s="2">
         <v>83</v>
@@ -12917,13 +12856,13 @@
         <v>72</v>
       </c>
       <c r="K113" t="s" s="2">
-        <v>139</v>
+        <v>113</v>
       </c>
       <c r="L113" t="s" s="2">
-        <v>340</v>
+        <v>346</v>
       </c>
       <c r="M113" t="s" s="2">
-        <v>341</v>
+        <v>347</v>
       </c>
       <c r="N113" s="2"/>
       <c r="O113" s="2"/>
@@ -12974,10 +12913,10 @@
         <v>72</v>
       </c>
       <c r="AF113" t="s" s="2">
-        <v>339</v>
+        <v>345</v>
       </c>
       <c r="AG113" t="s" s="2">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="AH113" t="s" s="2">
         <v>83</v>
@@ -12991,10 +12930,10 @@
     </row>
     <row r="114">
       <c r="A114" t="s" s="2">
-        <v>342</v>
+        <v>348</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>342</v>
+        <v>348</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
@@ -13002,10 +12941,10 @@
       </c>
       <c r="E114" s="2"/>
       <c r="F114" t="s" s="2">
-        <v>73</v>
+        <v>83</v>
       </c>
       <c r="G114" t="s" s="2">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="H114" t="s" s="2">
         <v>72</v>
@@ -13017,13 +12956,13 @@
         <v>72</v>
       </c>
       <c r="K114" t="s" s="2">
-        <v>84</v>
+        <v>113</v>
       </c>
       <c r="L114" t="s" s="2">
-        <v>343</v>
+        <v>349</v>
       </c>
       <c r="M114" t="s" s="2">
-        <v>344</v>
+        <v>350</v>
       </c>
       <c r="N114" s="2"/>
       <c r="O114" s="2"/>
@@ -13074,13 +13013,13 @@
         <v>72</v>
       </c>
       <c r="AF114" t="s" s="2">
-        <v>342</v>
+        <v>348</v>
       </c>
       <c r="AG114" t="s" s="2">
-        <v>73</v>
+        <v>83</v>
       </c>
       <c r="AH114" t="s" s="2">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="AI114" t="s" s="2">
         <v>72</v>
@@ -13091,10 +13030,10 @@
     </row>
     <row r="115">
       <c r="A115" t="s" s="2">
-        <v>345</v>
+        <v>351</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>345</v>
+        <v>351</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
@@ -13105,7 +13044,7 @@
         <v>83</v>
       </c>
       <c r="G115" t="s" s="2">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="H115" t="s" s="2">
         <v>72</v>
@@ -13117,13 +13056,13 @@
         <v>72</v>
       </c>
       <c r="K115" t="s" s="2">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="L115" t="s" s="2">
-        <v>346</v>
+        <v>352</v>
       </c>
       <c r="M115" t="s" s="2">
-        <v>347</v>
+        <v>353</v>
       </c>
       <c r="N115" s="2"/>
       <c r="O115" s="2"/>
@@ -13174,27 +13113,27 @@
         <v>72</v>
       </c>
       <c r="AF115" t="s" s="2">
-        <v>345</v>
+        <v>351</v>
       </c>
       <c r="AG115" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH115" t="s" s="2">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="AI115" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AJ115" t="s" s="2">
-        <v>72</v>
+        <v>81</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="s" s="2">
-        <v>348</v>
+        <v>354</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>348</v>
+        <v>354</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
@@ -13202,7 +13141,7 @@
       </c>
       <c r="E116" s="2"/>
       <c r="F116" t="s" s="2">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="G116" t="s" s="2">
         <v>83</v>
@@ -13217,13 +13156,13 @@
         <v>72</v>
       </c>
       <c r="K116" t="s" s="2">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="L116" t="s" s="2">
-        <v>349</v>
+        <v>85</v>
       </c>
       <c r="M116" t="s" s="2">
-        <v>350</v>
+        <v>86</v>
       </c>
       <c r="N116" s="2"/>
       <c r="O116" s="2"/>
@@ -13274,10 +13213,10 @@
         <v>72</v>
       </c>
       <c r="AF116" t="s" s="2">
-        <v>348</v>
+        <v>87</v>
       </c>
       <c r="AG116" t="s" s="2">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="AH116" t="s" s="2">
         <v>83</v>
@@ -13286,26 +13225,26 @@
         <v>72</v>
       </c>
       <c r="AJ116" t="s" s="2">
-        <v>81</v>
+        <v>72</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="s" s="2">
-        <v>351</v>
+        <v>355</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>351</v>
+        <v>355</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
-        <v>72</v>
+        <v>89</v>
       </c>
       <c r="E117" s="2"/>
       <c r="F117" t="s" s="2">
         <v>73</v>
       </c>
       <c r="G117" t="s" s="2">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="H117" t="s" s="2">
         <v>72</v>
@@ -13317,15 +13256,17 @@
         <v>72</v>
       </c>
       <c r="K117" t="s" s="2">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="L117" t="s" s="2">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="M117" t="s" s="2">
-        <v>86</v>
-      </c>
-      <c r="N117" s="2"/>
+        <v>92</v>
+      </c>
+      <c r="N117" t="s" s="2">
+        <v>93</v>
+      </c>
       <c r="O117" s="2"/>
       <c r="P117" t="s" s="2">
         <v>72</v>
@@ -13362,43 +13303,43 @@
         <v>72</v>
       </c>
       <c r="AB117" t="s" s="2">
-        <v>72</v>
+        <v>94</v>
       </c>
       <c r="AC117" t="s" s="2">
-        <v>72</v>
+        <v>95</v>
       </c>
       <c r="AD117" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AE117" t="s" s="2">
-        <v>72</v>
+        <v>96</v>
       </c>
       <c r="AF117" t="s" s="2">
-        <v>87</v>
+        <v>97</v>
       </c>
       <c r="AG117" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AH117" t="s" s="2">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="AI117" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AJ117" t="s" s="2">
-        <v>72</v>
+        <v>98</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="s" s="2">
-        <v>352</v>
+        <v>356</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>352</v>
+        <v>356</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
-        <v>89</v>
+        <v>100</v>
       </c>
       <c r="E118" s="2"/>
       <c r="F118" t="s" s="2">
@@ -13411,24 +13352,26 @@
         <v>72</v>
       </c>
       <c r="I118" t="s" s="2">
-        <v>72</v>
+        <v>101</v>
       </c>
       <c r="J118" t="s" s="2">
-        <v>72</v>
+        <v>101</v>
       </c>
       <c r="K118" t="s" s="2">
         <v>90</v>
       </c>
       <c r="L118" t="s" s="2">
-        <v>91</v>
+        <v>102</v>
       </c>
       <c r="M118" t="s" s="2">
-        <v>92</v>
+        <v>103</v>
       </c>
       <c r="N118" t="s" s="2">
         <v>93</v>
       </c>
-      <c r="O118" s="2"/>
+      <c r="O118" t="s" s="2">
+        <v>104</v>
+      </c>
       <c r="P118" t="s" s="2">
         <v>72</v>
       </c>
@@ -13464,19 +13407,19 @@
         <v>72</v>
       </c>
       <c r="AB118" t="s" s="2">
-        <v>94</v>
+        <v>72</v>
       </c>
       <c r="AC118" t="s" s="2">
-        <v>95</v>
+        <v>72</v>
       </c>
       <c r="AD118" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AE118" t="s" s="2">
-        <v>96</v>
+        <v>72</v>
       </c>
       <c r="AF118" t="s" s="2">
-        <v>97</v>
+        <v>105</v>
       </c>
       <c r="AG118" t="s" s="2">
         <v>73</v>
@@ -13493,46 +13436,42 @@
     </row>
     <row r="119">
       <c r="A119" t="s" s="2">
-        <v>353</v>
+        <v>357</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>353</v>
+        <v>357</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
-        <v>100</v>
+        <v>72</v>
       </c>
       <c r="E119" s="2"/>
       <c r="F119" t="s" s="2">
-        <v>73</v>
+        <v>83</v>
       </c>
       <c r="G119" t="s" s="2">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="H119" t="s" s="2">
         <v>72</v>
       </c>
       <c r="I119" t="s" s="2">
-        <v>101</v>
+        <v>72</v>
       </c>
       <c r="J119" t="s" s="2">
-        <v>101</v>
+        <v>72</v>
       </c>
       <c r="K119" t="s" s="2">
-        <v>90</v>
+        <v>113</v>
       </c>
       <c r="L119" t="s" s="2">
-        <v>102</v>
+        <v>358</v>
       </c>
       <c r="M119" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="N119" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="O119" t="s" s="2">
-        <v>104</v>
-      </c>
+        <v>359</v>
+      </c>
+      <c r="N119" s="2"/>
+      <c r="O119" s="2"/>
       <c r="P119" t="s" s="2">
         <v>72</v>
       </c>
@@ -13580,27 +13519,27 @@
         <v>72</v>
       </c>
       <c r="AF119" t="s" s="2">
-        <v>105</v>
+        <v>357</v>
       </c>
       <c r="AG119" t="s" s="2">
-        <v>73</v>
+        <v>83</v>
       </c>
       <c r="AH119" t="s" s="2">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="AI119" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AJ119" t="s" s="2">
-        <v>98</v>
+        <v>72</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="s" s="2">
-        <v>354</v>
+        <v>360</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>354</v>
+        <v>360</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
@@ -13608,7 +13547,7 @@
       </c>
       <c r="E120" s="2"/>
       <c r="F120" t="s" s="2">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="G120" t="s" s="2">
         <v>83</v>
@@ -13623,13 +13562,13 @@
         <v>72</v>
       </c>
       <c r="K120" t="s" s="2">
-        <v>355</v>
+        <v>113</v>
       </c>
       <c r="L120" t="s" s="2">
-        <v>356</v>
+        <v>361</v>
       </c>
       <c r="M120" t="s" s="2">
-        <v>357</v>
+        <v>362</v>
       </c>
       <c r="N120" s="2"/>
       <c r="O120" s="2"/>
@@ -13680,10 +13619,10 @@
         <v>72</v>
       </c>
       <c r="AF120" t="s" s="2">
-        <v>354</v>
+        <v>360</v>
       </c>
       <c r="AG120" t="s" s="2">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="AH120" t="s" s="2">
         <v>83</v>
@@ -13697,10 +13636,10 @@
     </row>
     <row r="121">
       <c r="A121" t="s" s="2">
-        <v>358</v>
+        <v>363</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>358</v>
+        <v>363</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
@@ -13708,7 +13647,7 @@
       </c>
       <c r="E121" s="2"/>
       <c r="F121" t="s" s="2">
-        <v>73</v>
+        <v>83</v>
       </c>
       <c r="G121" t="s" s="2">
         <v>83</v>
@@ -13723,13 +13662,13 @@
         <v>72</v>
       </c>
       <c r="K121" t="s" s="2">
-        <v>355</v>
+        <v>113</v>
       </c>
       <c r="L121" t="s" s="2">
-        <v>359</v>
+        <v>364</v>
       </c>
       <c r="M121" t="s" s="2">
-        <v>360</v>
+        <v>365</v>
       </c>
       <c r="N121" s="2"/>
       <c r="O121" s="2"/>
@@ -13780,10 +13719,10 @@
         <v>72</v>
       </c>
       <c r="AF121" t="s" s="2">
-        <v>358</v>
+        <v>363</v>
       </c>
       <c r="AG121" t="s" s="2">
-        <v>73</v>
+        <v>83</v>
       </c>
       <c r="AH121" t="s" s="2">
         <v>83</v>
@@ -13797,10 +13736,10 @@
     </row>
     <row r="122">
       <c r="A122" t="s" s="2">
-        <v>361</v>
+        <v>366</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>361</v>
+        <v>366</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
@@ -13823,13 +13762,13 @@
         <v>72</v>
       </c>
       <c r="K122" t="s" s="2">
-        <v>84</v>
+        <v>113</v>
       </c>
       <c r="L122" t="s" s="2">
-        <v>362</v>
+        <v>367</v>
       </c>
       <c r="M122" t="s" s="2">
-        <v>363</v>
+        <v>368</v>
       </c>
       <c r="N122" s="2"/>
       <c r="O122" s="2"/>
@@ -13880,7 +13819,7 @@
         <v>72</v>
       </c>
       <c r="AF122" t="s" s="2">
-        <v>361</v>
+        <v>366</v>
       </c>
       <c r="AG122" t="s" s="2">
         <v>73</v>
@@ -13897,10 +13836,10 @@
     </row>
     <row r="123">
       <c r="A123" t="s" s="2">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="C123" s="2"/>
       <c r="D123" t="s" s="2">
@@ -13908,7 +13847,7 @@
       </c>
       <c r="E123" s="2"/>
       <c r="F123" t="s" s="2">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="G123" t="s" s="2">
         <v>83</v>
@@ -13923,13 +13862,13 @@
         <v>72</v>
       </c>
       <c r="K123" t="s" s="2">
-        <v>84</v>
+        <v>113</v>
       </c>
       <c r="L123" t="s" s="2">
-        <v>365</v>
+        <v>370</v>
       </c>
       <c r="M123" t="s" s="2">
-        <v>366</v>
+        <v>371</v>
       </c>
       <c r="N123" s="2"/>
       <c r="O123" s="2"/>
@@ -13980,10 +13919,10 @@
         <v>72</v>
       </c>
       <c r="AF123" t="s" s="2">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="AG123" t="s" s="2">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="AH123" t="s" s="2">
         <v>83</v>
@@ -13992,106 +13931,6 @@
         <v>72</v>
       </c>
       <c r="AJ123" t="s" s="2">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" t="s" s="2">
-        <v>367</v>
-      </c>
-      <c r="B124" t="s" s="2">
-        <v>367</v>
-      </c>
-      <c r="C124" s="2"/>
-      <c r="D124" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="E124" s="2"/>
-      <c r="F124" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="G124" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="H124" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="I124" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="J124" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="K124" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="L124" t="s" s="2">
-        <v>368</v>
-      </c>
-      <c r="M124" t="s" s="2">
-        <v>369</v>
-      </c>
-      <c r="N124" s="2"/>
-      <c r="O124" s="2"/>
-      <c r="P124" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="Q124" s="2"/>
-      <c r="R124" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="S124" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="T124" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="U124" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="V124" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="W124" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="X124" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="Y124" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="Z124" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AA124" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AB124" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AC124" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AD124" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AE124" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AF124" t="s" s="2">
-        <v>367</v>
-      </c>
-      <c r="AG124" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AH124" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AI124" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AJ124" t="s" s="2">
         <v>72</v>
       </c>
     </row>

--- a/StructureDefinition-SEEHDSLMAlertInformation.xlsx
+++ b/StructureDefinition-SEEHDSLMAlertInformation.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.3.3</t>
+    <t>0.5.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-09T07:52:45+00:00</t>
+    <t>2026-10-12T12:51:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-SEEHDSLMAlertInformation.xlsx
+++ b/StructureDefinition-SEEHDSLMAlertInformation.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-12T12:51:47+00:00</t>
+    <t>2026-10-12T13:38:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-SEEHDSLMAlertInformation.xlsx
+++ b/StructureDefinition-SEEHDSLMAlertInformation.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3903" uniqueCount="372">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3903" uniqueCount="374">
   <si>
     <t>Property</t>
   </si>
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.5.0</t>
+    <t>0.6.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-12T13:38:08+00:00</t>
+    <t>2026-10-15T17:10:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -665,6 +665,10 @@
     <t>AlertInformationBodyType — uppmärksamhetsinformationens informationsinnehåll.
 Exakt en av hypersensitivity, seriousDisease, treatment, communicableDisease,
 restrictionOfCare, unstructuredAlertInformation ska anges (XOR).</t>
+  </si>
+  <si>
+    <t>getalertinformation-body-choice:En och endast en av hypersensitivity, seriousDisease, treatment, communicableDisease, restrictionOfCare och unstructuredAlertInformation ska anges {hypersensitivity.combine(seriousDisease).combine(treatment).combine(communicableDisease).combine(restrictionOfCare).combine(unstructuredAlertInformation).count() = 1}
+ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}</t>
   </si>
   <si>
     <t>SEEHDSLMAlertInformation.alertInformation.alertInformationBody.id</t>
@@ -813,6 +817,10 @@
   </si>
   <si>
     <t>Mer detaljerad information om läkemedelsöverkänslighet.</t>
+  </si>
+  <si>
+    <t>getalertinformation-substance-choice:Antingen atcSubstance eller både nonATCSubstance och nonATCSubstanceComment ska anges {(atcSubstance.exists() and nonATCSubstance.empty() and nonATCSubstanceComment.empty()) or (atcSubstance.empty() and nonATCSubstance.exists() and nonATCSubstanceComment.exists())}
+ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}</t>
   </si>
   <si>
     <t>SEEHDSLMAlertInformation.alertInformation.alertInformationBody.hypersensitivity.pharmaceuticalHypersensitivity.id</t>
@@ -6265,15 +6273,15 @@
         <v>72</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>81</v>
+        <v>208</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -6370,10 +6378,10 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -6472,10 +6480,10 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -6576,10 +6584,10 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -6605,10 +6613,10 @@
         <v>146</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" s="2"/>
@@ -6659,7 +6667,7 @@
         <v>72</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>83</v>
@@ -6676,10 +6684,10 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -6702,13 +6710,13 @@
         <v>72</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" s="2"/>
@@ -6759,7 +6767,7 @@
         <v>72</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>73</v>
@@ -6776,10 +6784,10 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -6805,10 +6813,10 @@
         <v>123</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" s="2"/>
@@ -6859,7 +6867,7 @@
         <v>72</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>73</v>
@@ -6876,10 +6884,10 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -6902,13 +6910,13 @@
         <v>72</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="N54" s="2"/>
       <c r="O54" s="2"/>
@@ -6959,7 +6967,7 @@
         <v>72</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>83</v>
@@ -6976,10 +6984,10 @@
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -7005,10 +7013,10 @@
         <v>113</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="N55" s="2"/>
       <c r="O55" s="2"/>
@@ -7059,7 +7067,7 @@
         <v>72</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>73</v>
@@ -7076,10 +7084,10 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -7105,10 +7113,10 @@
         <v>123</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="N56" s="2"/>
       <c r="O56" s="2"/>
@@ -7159,7 +7167,7 @@
         <v>72</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>73</v>
@@ -7176,10 +7184,10 @@
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -7205,10 +7213,10 @@
         <v>113</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="N57" s="2"/>
       <c r="O57" s="2"/>
@@ -7259,7 +7267,7 @@
         <v>72</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>73</v>
@@ -7276,10 +7284,10 @@
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -7305,10 +7313,10 @@
         <v>78</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="N58" s="2"/>
       <c r="O58" s="2"/>
@@ -7359,7 +7367,7 @@
         <v>72</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>73</v>
@@ -7376,10 +7384,10 @@
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -7476,10 +7484,10 @@
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -7578,10 +7586,10 @@
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -7682,10 +7690,10 @@
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -7711,10 +7719,10 @@
         <v>146</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="N62" s="2"/>
       <c r="O62" s="2"/>
@@ -7765,7 +7773,7 @@
         <v>72</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>73</v>
@@ -7782,10 +7790,10 @@
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -7811,10 +7819,10 @@
         <v>146</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="N63" s="2"/>
       <c r="O63" s="2"/>
@@ -7865,7 +7873,7 @@
         <v>72</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>73</v>
@@ -7882,10 +7890,10 @@
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -7911,10 +7919,10 @@
         <v>146</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="N64" s="2"/>
       <c r="O64" s="2"/>
@@ -7965,7 +7973,7 @@
         <v>72</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>73</v>
@@ -7982,10 +7990,10 @@
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -8011,10 +8019,10 @@
         <v>78</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="N65" s="2"/>
       <c r="O65" s="2"/>
@@ -8065,7 +8073,7 @@
         <v>72</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>73</v>
@@ -8077,15 +8085,15 @@
         <v>72</v>
       </c>
       <c r="AJ65" t="s" s="2">
-        <v>81</v>
+        <v>253</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -8182,10 +8190,10 @@
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -8284,10 +8292,10 @@
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -8388,10 +8396,10 @@
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -8417,10 +8425,10 @@
         <v>146</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="N69" s="2"/>
       <c r="O69" s="2"/>
@@ -8471,7 +8479,7 @@
         <v>72</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>73</v>
@@ -8488,10 +8496,10 @@
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -8517,10 +8525,10 @@
         <v>113</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="N70" s="2"/>
       <c r="O70" s="2"/>
@@ -8571,7 +8579,7 @@
         <v>72</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>73</v>
@@ -8588,10 +8596,10 @@
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -8617,10 +8625,10 @@
         <v>113</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="N71" s="2"/>
       <c r="O71" s="2"/>
@@ -8671,7 +8679,7 @@
         <v>72</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>73</v>
@@ -8688,10 +8696,10 @@
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -8717,10 +8725,10 @@
         <v>146</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="N72" s="2"/>
       <c r="O72" s="2"/>
@@ -8771,7 +8779,7 @@
         <v>72</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>73</v>
@@ -8788,10 +8796,10 @@
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -8817,10 +8825,10 @@
         <v>78</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="N73" s="2"/>
       <c r="O73" s="2"/>
@@ -8871,7 +8879,7 @@
         <v>72</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>73</v>
@@ -8888,10 +8896,10 @@
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -8988,10 +8996,10 @@
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -9090,10 +9098,10 @@
     </row>
     <row r="76">
       <c r="A76" t="s" s="2">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -9194,10 +9202,10 @@
     </row>
     <row r="77">
       <c r="A77" t="s" s="2">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -9223,10 +9231,10 @@
         <v>113</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="N77" s="2"/>
       <c r="O77" s="2"/>
@@ -9277,7 +9285,7 @@
         <v>72</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>73</v>
@@ -9294,10 +9302,10 @@
     </row>
     <row r="78">
       <c r="A78" t="s" s="2">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -9323,10 +9331,10 @@
         <v>146</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="N78" s="2"/>
       <c r="O78" s="2"/>
@@ -9377,7 +9385,7 @@
         <v>72</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>73</v>
@@ -9394,10 +9402,10 @@
     </row>
     <row r="79">
       <c r="A79" t="s" s="2">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -9423,10 +9431,10 @@
         <v>78</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="N79" s="2"/>
       <c r="O79" s="2"/>
@@ -9477,7 +9485,7 @@
         <v>72</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>73</v>
@@ -9494,10 +9502,10 @@
     </row>
     <row r="80">
       <c r="A80" t="s" s="2">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -9594,10 +9602,10 @@
     </row>
     <row r="81">
       <c r="A81" t="s" s="2">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -9696,10 +9704,10 @@
     </row>
     <row r="82">
       <c r="A82" t="s" s="2">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -9800,10 +9808,10 @@
     </row>
     <row r="83">
       <c r="A83" t="s" s="2">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -9829,10 +9837,10 @@
         <v>146</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="N83" s="2"/>
       <c r="O83" s="2"/>
@@ -9883,7 +9891,7 @@
         <v>72</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>83</v>
@@ -9900,10 +9908,10 @@
     </row>
     <row r="84">
       <c r="A84" t="s" s="2">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -9929,10 +9937,10 @@
         <v>78</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="N84" s="2"/>
       <c r="O84" s="2"/>
@@ -9983,7 +9991,7 @@
         <v>72</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>73</v>
@@ -10000,10 +10008,10 @@
     </row>
     <row r="85">
       <c r="A85" t="s" s="2">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -10100,10 +10108,10 @@
     </row>
     <row r="86">
       <c r="A86" t="s" s="2">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -10202,10 +10210,10 @@
     </row>
     <row r="87">
       <c r="A87" t="s" s="2">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -10306,10 +10314,10 @@
     </row>
     <row r="88">
       <c r="A88" t="s" s="2">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -10335,10 +10343,10 @@
         <v>113</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="N88" s="2"/>
       <c r="O88" s="2"/>
@@ -10389,7 +10397,7 @@
         <v>72</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>83</v>
@@ -10406,10 +10414,10 @@
     </row>
     <row r="89">
       <c r="A89" t="s" s="2">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -10435,10 +10443,10 @@
         <v>146</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="N89" s="2"/>
       <c r="O89" s="2"/>
@@ -10489,7 +10497,7 @@
         <v>72</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>73</v>
@@ -10506,10 +10514,10 @@
     </row>
     <row r="90">
       <c r="A90" t="s" s="2">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -10535,10 +10543,10 @@
         <v>146</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="N90" s="2"/>
       <c r="O90" s="2"/>
@@ -10589,7 +10597,7 @@
         <v>72</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>73</v>
@@ -10606,10 +10614,10 @@
     </row>
     <row r="91">
       <c r="A91" t="s" s="2">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -10635,10 +10643,10 @@
         <v>78</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="N91" s="2"/>
       <c r="O91" s="2"/>
@@ -10689,7 +10697,7 @@
         <v>72</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>73</v>
@@ -10706,10 +10714,10 @@
     </row>
     <row r="92">
       <c r="A92" t="s" s="2">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -10806,10 +10814,10 @@
     </row>
     <row r="93">
       <c r="A93" t="s" s="2">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -10908,10 +10916,10 @@
     </row>
     <row r="94">
       <c r="A94" t="s" s="2">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -11012,10 +11020,10 @@
     </row>
     <row r="95">
       <c r="A95" t="s" s="2">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -11041,10 +11049,10 @@
         <v>146</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="N95" s="2"/>
       <c r="O95" s="2"/>
@@ -11095,7 +11103,7 @@
         <v>72</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>83</v>
@@ -11112,10 +11120,10 @@
     </row>
     <row r="96">
       <c r="A96" t="s" s="2">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -11141,10 +11149,10 @@
         <v>146</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="N96" s="2"/>
       <c r="O96" s="2"/>
@@ -11195,7 +11203,7 @@
         <v>72</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>73</v>
@@ -11212,10 +11220,10 @@
     </row>
     <row r="97">
       <c r="A97" t="s" s="2">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -11241,10 +11249,10 @@
         <v>78</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="N97" s="2"/>
       <c r="O97" s="2"/>
@@ -11295,7 +11303,7 @@
         <v>72</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>73</v>
@@ -11312,10 +11320,10 @@
     </row>
     <row r="98">
       <c r="A98" t="s" s="2">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -11412,10 +11420,10 @@
     </row>
     <row r="99">
       <c r="A99" t="s" s="2">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -11514,10 +11522,10 @@
     </row>
     <row r="100">
       <c r="A100" t="s" s="2">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -11618,10 +11626,10 @@
     </row>
     <row r="101">
       <c r="A101" t="s" s="2">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -11647,10 +11655,10 @@
         <v>113</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="N101" s="2"/>
       <c r="O101" s="2"/>
@@ -11701,7 +11709,7 @@
         <v>72</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>83</v>
@@ -11718,10 +11726,10 @@
     </row>
     <row r="102">
       <c r="A102" t="s" s="2">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -11747,10 +11755,10 @@
         <v>78</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="N102" s="2"/>
       <c r="O102" s="2"/>
@@ -11801,7 +11809,7 @@
         <v>72</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>73</v>
@@ -11818,10 +11826,10 @@
     </row>
     <row r="103">
       <c r="A103" t="s" s="2">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -11918,10 +11926,10 @@
     </row>
     <row r="104">
       <c r="A104" t="s" s="2">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -12020,10 +12028,10 @@
     </row>
     <row r="105">
       <c r="A105" t="s" s="2">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -12124,10 +12132,10 @@
     </row>
     <row r="106">
       <c r="A106" t="s" s="2">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -12153,10 +12161,10 @@
         <v>113</v>
       </c>
       <c r="L106" t="s" s="2">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="M106" t="s" s="2">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="N106" s="2"/>
       <c r="O106" s="2"/>
@@ -12207,7 +12215,7 @@
         <v>72</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>83</v>
@@ -12224,10 +12232,10 @@
     </row>
     <row r="107">
       <c r="A107" t="s" s="2">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -12253,10 +12261,10 @@
         <v>113</v>
       </c>
       <c r="L107" t="s" s="2">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="M107" t="s" s="2">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="N107" s="2"/>
       <c r="O107" s="2"/>
@@ -12307,7 +12315,7 @@
         <v>72</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>83</v>
@@ -12324,10 +12332,10 @@
     </row>
     <row r="108">
       <c r="A108" t="s" s="2">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -12353,10 +12361,10 @@
         <v>78</v>
       </c>
       <c r="L108" t="s" s="2">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="M108" t="s" s="2">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="N108" s="2"/>
       <c r="O108" s="2"/>
@@ -12407,7 +12415,7 @@
         <v>72</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>73</v>
@@ -12424,10 +12432,10 @@
     </row>
     <row r="109">
       <c r="A109" t="s" s="2">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -12524,10 +12532,10 @@
     </row>
     <row r="110">
       <c r="A110" t="s" s="2">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -12626,10 +12634,10 @@
     </row>
     <row r="111">
       <c r="A111" t="s" s="2">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -12730,10 +12738,10 @@
     </row>
     <row r="112">
       <c r="A112" t="s" s="2">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -12759,10 +12767,10 @@
         <v>146</v>
       </c>
       <c r="L112" t="s" s="2">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="M112" t="s" s="2">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="N112" s="2"/>
       <c r="O112" s="2"/>
@@ -12813,7 +12821,7 @@
         <v>72</v>
       </c>
       <c r="AF112" t="s" s="2">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="AG112" t="s" s="2">
         <v>83</v>
@@ -12830,10 +12838,10 @@
     </row>
     <row r="113">
       <c r="A113" t="s" s="2">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -12859,10 +12867,10 @@
         <v>113</v>
       </c>
       <c r="L113" t="s" s="2">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="M113" t="s" s="2">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="N113" s="2"/>
       <c r="O113" s="2"/>
@@ -12913,7 +12921,7 @@
         <v>72</v>
       </c>
       <c r="AF113" t="s" s="2">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="AG113" t="s" s="2">
         <v>73</v>
@@ -12930,10 +12938,10 @@
     </row>
     <row r="114">
       <c r="A114" t="s" s="2">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
@@ -12959,10 +12967,10 @@
         <v>113</v>
       </c>
       <c r="L114" t="s" s="2">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="M114" t="s" s="2">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="N114" s="2"/>
       <c r="O114" s="2"/>
@@ -13013,7 +13021,7 @@
         <v>72</v>
       </c>
       <c r="AF114" t="s" s="2">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="AG114" t="s" s="2">
         <v>83</v>
@@ -13030,10 +13038,10 @@
     </row>
     <row r="115">
       <c r="A115" t="s" s="2">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
@@ -13059,10 +13067,10 @@
         <v>78</v>
       </c>
       <c r="L115" t="s" s="2">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="M115" t="s" s="2">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="N115" s="2"/>
       <c r="O115" s="2"/>
@@ -13113,7 +13121,7 @@
         <v>72</v>
       </c>
       <c r="AF115" t="s" s="2">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="AG115" t="s" s="2">
         <v>83</v>
@@ -13130,10 +13138,10 @@
     </row>
     <row r="116">
       <c r="A116" t="s" s="2">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
@@ -13230,10 +13238,10 @@
     </row>
     <row r="117">
       <c r="A117" t="s" s="2">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
@@ -13332,10 +13340,10 @@
     </row>
     <row r="118">
       <c r="A118" t="s" s="2">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
@@ -13436,10 +13444,10 @@
     </row>
     <row r="119">
       <c r="A119" t="s" s="2">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
@@ -13465,10 +13473,10 @@
         <v>113</v>
       </c>
       <c r="L119" t="s" s="2">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="M119" t="s" s="2">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="N119" s="2"/>
       <c r="O119" s="2"/>
@@ -13519,7 +13527,7 @@
         <v>72</v>
       </c>
       <c r="AF119" t="s" s="2">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="AG119" t="s" s="2">
         <v>83</v>
@@ -13536,10 +13544,10 @@
     </row>
     <row r="120">
       <c r="A120" t="s" s="2">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
@@ -13565,10 +13573,10 @@
         <v>113</v>
       </c>
       <c r="L120" t="s" s="2">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="M120" t="s" s="2">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="N120" s="2"/>
       <c r="O120" s="2"/>
@@ -13619,7 +13627,7 @@
         <v>72</v>
       </c>
       <c r="AF120" t="s" s="2">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="AG120" t="s" s="2">
         <v>73</v>
@@ -13636,10 +13644,10 @@
     </row>
     <row r="121">
       <c r="A121" t="s" s="2">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
@@ -13665,10 +13673,10 @@
         <v>113</v>
       </c>
       <c r="L121" t="s" s="2">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="M121" t="s" s="2">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="N121" s="2"/>
       <c r="O121" s="2"/>
@@ -13719,7 +13727,7 @@
         <v>72</v>
       </c>
       <c r="AF121" t="s" s="2">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="AG121" t="s" s="2">
         <v>83</v>
@@ -13736,10 +13744,10 @@
     </row>
     <row r="122">
       <c r="A122" t="s" s="2">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
@@ -13765,10 +13773,10 @@
         <v>113</v>
       </c>
       <c r="L122" t="s" s="2">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="M122" t="s" s="2">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="N122" s="2"/>
       <c r="O122" s="2"/>
@@ -13819,7 +13827,7 @@
         <v>72</v>
       </c>
       <c r="AF122" t="s" s="2">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="AG122" t="s" s="2">
         <v>73</v>
@@ -13836,10 +13844,10 @@
     </row>
     <row r="123">
       <c r="A123" t="s" s="2">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="C123" s="2"/>
       <c r="D123" t="s" s="2">
@@ -13865,10 +13873,10 @@
         <v>113</v>
       </c>
       <c r="L123" t="s" s="2">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="M123" t="s" s="2">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="N123" s="2"/>
       <c r="O123" s="2"/>
@@ -13919,7 +13927,7 @@
         <v>72</v>
       </c>
       <c r="AF123" t="s" s="2">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="AG123" t="s" s="2">
         <v>73</v>

--- a/StructureDefinition-SEEHDSLMAlertInformation.xlsx
+++ b/StructureDefinition-SEEHDSLMAlertInformation.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-15T17:10:15+00:00</t>
+    <t>2026-10-15T18:03:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-SEEHDSLMAlertInformation.xlsx
+++ b/StructureDefinition-SEEHDSLMAlertInformation.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.6.0</t>
+    <t>0.7.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-15T18:03:33+00:00</t>
+    <t>2026-10-26T15:58:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
